--- a/data/materials01.xlsx
+++ b/data/materials01.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C0BD76-A50F-4743-9658-D173E2686C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A928350-DBBB-44FD-9CCA-C7AA67243B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용방법" sheetId="1" r:id="rId1"/>
@@ -3248,7 +3248,7 @@
         <v>370</v>
       </c>
       <c r="J20">
-        <v>543.1</v>
+        <v>6</v>
       </c>
       <c r="L20" t="s">
         <v>89</v>
@@ -4699,7 +4699,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N66 A68:N88 A67:F67 H67:N67" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N19 A68:N88 A67:F67 H67:N67 A21:N66 A20:I20 K20:N20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/materials01.xlsx
+++ b/data/materials01.xlsx
@@ -483,7 +483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -619,7 +619,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Level 1 (≥10000)</v>
+        <v>Level 2 (≥1000)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>인조대리석</v>
+      </c>
+      <c r="D4" t="str">
+        <v>artificial_marble</v>
+      </c>
+      <c r="E4" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F4" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G4">
+        <v>6669</v>
+      </c>
+      <c r="H4" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I4">
+        <v>1900</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="L4" t="str">
+        <v>국가 LCI DB</v>
       </c>
     </row>
     <row r="5">
@@ -630,10 +657,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C5" t="str">
-        <v>인조대리석</v>
+        <v>EPDM</v>
       </c>
       <c r="D5" t="str">
-        <v>artificial_marble</v>
+        <v>epdm</v>
       </c>
       <c r="E5" t="str">
         <v>finishing</v>
@@ -642,19 +669,19 @@
         <v>마감재</v>
       </c>
       <c r="G5">
-        <v>6669</v>
+        <v>5570</v>
       </c>
       <c r="H5" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I5">
-        <v>1900</v>
+        <v>1333</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L5" t="str">
-        <v>국가 LCI DB</v>
+        <v>EC3</v>
       </c>
     </row>
     <row r="6">
@@ -665,10 +692,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C6" t="str">
-        <v>EPDM</v>
+        <v>에폭시수지</v>
       </c>
       <c r="D6" t="str">
-        <v>epdm</v>
+        <v>epoxy</v>
       </c>
       <c r="E6" t="str">
         <v>finishing</v>
@@ -677,19 +704,19 @@
         <v>마감재</v>
       </c>
       <c r="G6">
-        <v>5570</v>
+        <v>4860</v>
       </c>
       <c r="H6" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I6">
-        <v>1333</v>
+        <v>3036</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L6" t="str">
-        <v>EC3</v>
+        <v>국가 LCI DB</v>
       </c>
     </row>
     <row r="7">
@@ -700,31 +727,37 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C7" t="str">
-        <v>에폭시수지</v>
+        <v>재활용철근</v>
       </c>
       <c r="D7" t="str">
-        <v>epoxy</v>
+        <v>recycled rebar</v>
       </c>
       <c r="E7" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F7" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G7">
-        <v>4860</v>
+        <v>3438.3</v>
       </c>
       <c r="H7" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I7">
-        <v>3036</v>
+        <v>7850</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>3.2</v>
+      </c>
+      <c r="K7" t="str">
+        <v>○</v>
       </c>
       <c r="L7" t="str">
         <v>국가 LCI DB</v>
+      </c>
+      <c r="M7" t="str">
+        <v>@200 적용,상하부 2단, 25 kg/㎡</v>
       </c>
     </row>
     <row r="8">
@@ -735,37 +768,34 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C8" t="str">
-        <v>재활용철근</v>
+        <v>고무바닥재</v>
       </c>
       <c r="D8" t="str">
-        <v>recycled rebar</v>
+        <v>rubber_flooring</v>
       </c>
       <c r="E8" t="str">
-        <v>structural</v>
+        <v>finishing</v>
       </c>
       <c r="F8" t="str">
-        <v>구조재</v>
+        <v>마감재</v>
       </c>
       <c r="G8">
-        <v>3438.3</v>
+        <v>3140</v>
       </c>
       <c r="H8" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I8">
-        <v>7850</v>
+        <v>1200</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
-      </c>
-      <c r="K8" t="str">
-        <v>○</v>
+        <v>6</v>
       </c>
       <c r="L8" t="str">
-        <v>국가 LCI DB</v>
-      </c>
-      <c r="M8" t="str">
-        <v>@200 적용,상하부 2단, 25 kg/㎡</v>
+        <v>EC3</v>
+      </c>
+      <c r="N8" t="str">
+        <v>(FLEXXER Rubber Flooring) 15.7 kgCO2e/m²(5mm) ÷ 0.005 = 3140 kgCO2e/m³</v>
       </c>
     </row>
     <row r="9">
@@ -776,10 +806,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C9" t="str">
-        <v>고무바닥재</v>
+        <v>우레탄방수</v>
       </c>
       <c r="D9" t="str">
-        <v>rubber_flooring</v>
+        <v>urethan</v>
       </c>
       <c r="E9" t="str">
         <v>finishing</v>
@@ -788,22 +818,19 @@
         <v>마감재</v>
       </c>
       <c r="G9">
-        <v>3140</v>
+        <v>2496</v>
       </c>
       <c r="H9" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I9">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L9" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N9" t="str">
-        <v>(FLEXXER Rubber Flooring) 15.7 kgCO2e/m²(5mm) ÷ 0.005 = 3140 kgCO2e/m³</v>
+        <v>국가 LCI DB</v>
       </c>
     </row>
     <row r="10">
@@ -814,10 +841,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C10" t="str">
-        <v>우레탄방수</v>
+        <v>재활용고무바닥재</v>
       </c>
       <c r="D10" t="str">
-        <v>urethan</v>
+        <v>recycled_rubber</v>
       </c>
       <c r="E10" t="str">
         <v>finishing</v>
@@ -826,19 +853,22 @@
         <v>마감재</v>
       </c>
       <c r="G10">
-        <v>2496</v>
+        <v>1638.75</v>
       </c>
       <c r="H10" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I10">
-        <v>1300</v>
+        <v>1050</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L10" t="str">
-        <v>국가 LCI DB</v>
+        <v>EC3</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Tarkett</v>
       </c>
     </row>
     <row r="11">
@@ -849,10 +879,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C11" t="str">
-        <v>재활용고무바닥재</v>
+        <v>포세린타일</v>
       </c>
       <c r="D11" t="str">
-        <v>recycled_rubber</v>
+        <v>porcelain_tile</v>
       </c>
       <c r="E11" t="str">
         <v>finishing</v>
@@ -861,22 +891,19 @@
         <v>마감재</v>
       </c>
       <c r="G11">
-        <v>1638.75</v>
+        <v>1540</v>
       </c>
       <c r="H11" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I11">
-        <v>1050</v>
+        <v>2200</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N11" t="str">
-        <v>Tarkett</v>
+        <v>ICE v3</v>
       </c>
     </row>
     <row r="12">
@@ -887,10 +914,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C12" t="str">
-        <v>포세린타일</v>
+        <v>이중바닥재</v>
       </c>
       <c r="D12" t="str">
-        <v>porcelain_tile</v>
+        <v>raised_access_floor</v>
       </c>
       <c r="E12" t="str">
         <v>finishing</v>
@@ -899,19 +926,22 @@
         <v>마감재</v>
       </c>
       <c r="G12">
-        <v>1540</v>
+        <v>1513.4</v>
       </c>
       <c r="H12" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I12">
-        <v>2200</v>
+        <v>433</v>
       </c>
       <c r="J12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L12" t="str">
-        <v>ICE v3</v>
+        <v>국내 EPD</v>
+      </c>
+      <c r="N12" t="str">
+        <v>LGM600 (무기질 황산칼슘ACC) [600x600x30T  SSP형]</v>
       </c>
     </row>
     <row r="13">
@@ -922,10 +952,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C13" t="str">
-        <v>이중바닥재</v>
+        <v>비닐시트</v>
       </c>
       <c r="D13" t="str">
-        <v>raised_access_floor</v>
+        <v>vinyl_sheet</v>
       </c>
       <c r="E13" t="str">
         <v>finishing</v>
@@ -934,22 +964,22 @@
         <v>마감재</v>
       </c>
       <c r="G13">
-        <v>1513.4</v>
+        <v>1486</v>
       </c>
       <c r="H13" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I13">
-        <v>433</v>
+        <v>1750</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="L13" t="str">
         <v>국내 EPD</v>
       </c>
       <c r="N13" t="str">
-        <v>LGM600 (무기질 황산칼슘ACC) [600x600x30T  SSP형]</v>
+        <v>엘엑스하우시스  Z:IN 마제스타 2.0</v>
       </c>
     </row>
     <row r="14">
@@ -960,10 +990,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C14" t="str">
-        <v>비닐시트</v>
+        <v>PVC타일</v>
       </c>
       <c r="D14" t="str">
-        <v>vinyl_sheet</v>
+        <v>pvc_tile</v>
       </c>
       <c r="E14" t="str">
         <v>finishing</v>
@@ -972,22 +1002,22 @@
         <v>마감재</v>
       </c>
       <c r="G14">
-        <v>1486</v>
+        <v>1386</v>
       </c>
       <c r="H14" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I14">
-        <v>1750</v>
+        <v>2200</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="str">
         <v>국내 EPD</v>
       </c>
       <c r="N14" t="str">
-        <v>엘엑스하우시스  Z:IN 마제스타 2.0</v>
+        <v>센스타일 트랜디(3t)  케이씨씨글라스</v>
       </c>
     </row>
     <row r="15">
@@ -998,10 +1028,10 @@
         <v>Level 2 (≥1000)</v>
       </c>
       <c r="C15" t="str">
-        <v>PVC타일</v>
+        <v>재활용플라스틱데크</v>
       </c>
       <c r="D15" t="str">
-        <v>pvc_tile</v>
+        <v>recycled_plastic_deck</v>
       </c>
       <c r="E15" t="str">
         <v>finishing</v>
@@ -1010,22 +1040,22 @@
         <v>마감재</v>
       </c>
       <c r="G15">
-        <v>1386</v>
+        <v>1163</v>
       </c>
       <c r="H15" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I15">
-        <v>2200</v>
+        <v>1050</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>23.2</v>
       </c>
       <c r="L15" t="str">
-        <v>국내 EPD</v>
+        <v>EC3</v>
       </c>
       <c r="N15" t="str">
-        <v>센스타일 트랜디(3t)  케이씨씨글라스</v>
+        <v>Fiberon Good Life Composite Decking 23.2</v>
       </c>
     </row>
     <row r="16">
@@ -1033,13 +1063,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Level 2 (≥1000)</v>
+        <v>Level 3 (≥100)</v>
       </c>
       <c r="C16" t="str">
-        <v>재활용플라스틱데크</v>
+        <v>바이오폴리우레탄바닥재</v>
       </c>
       <c r="D16" t="str">
-        <v>recycled_plastic_deck</v>
+        <v>bio_polyurethane_flooring</v>
       </c>
       <c r="E16" t="str">
         <v>finishing</v>
@@ -1048,22 +1078,22 @@
         <v>마감재</v>
       </c>
       <c r="G16">
-        <v>1163</v>
+        <v>923</v>
       </c>
       <c r="H16" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I16">
-        <v>1050</v>
+        <v>566</v>
       </c>
       <c r="J16">
-        <v>23.2</v>
+        <v>6</v>
       </c>
       <c r="L16" t="str">
-        <v>EC3</v>
+        <v>2050materials</v>
       </c>
       <c r="N16" t="str">
-        <v>Fiberon Good Life Composite Decking 23.2</v>
+        <v>Teknoflor Bio-Polyurethane Flooring</v>
       </c>
     </row>
     <row r="17">
@@ -1071,7 +1101,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Level 2 (≥1000)</v>
+        <v>Level 3 (≥100)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>진공단열재</v>
+      </c>
+      <c r="D17" t="str">
+        <v>vacuum_insulation_panel</v>
+      </c>
+      <c r="E17" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F17" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G17">
+        <v>683.98</v>
+      </c>
+      <c r="H17" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I17">
+        <v>1000</v>
+      </c>
+      <c r="J17">
+        <v>30</v>
+      </c>
+      <c r="L17" t="str">
+        <v>환경성적표지(주식회사 그린인슐레이터)</v>
+      </c>
+      <c r="N17" t="str">
+        <v>진공단열재(SUPERVAC)</v>
       </c>
     </row>
     <row r="18">
@@ -1082,10 +1142,10 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C18" t="str">
-        <v>바이오폴리우레탄바닥재</v>
+        <v>카펫타일</v>
       </c>
       <c r="D18" t="str">
-        <v>bio_polyurethane_flooring</v>
+        <v>carpet_tile</v>
       </c>
       <c r="E18" t="str">
         <v>finishing</v>
@@ -1094,22 +1154,22 @@
         <v>마감재</v>
       </c>
       <c r="G18">
-        <v>923</v>
+        <v>543.1</v>
       </c>
       <c r="H18" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I18">
-        <v>566</v>
+        <v>370</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L18" t="str">
-        <v>2050materials</v>
+        <v>국내EPD</v>
       </c>
       <c r="N18" t="str">
-        <v>Teknoflor Bio-Polyurethane Flooring</v>
+        <v>INFINI COLORS - tufted carpet tiles</v>
       </c>
     </row>
     <row r="19">
@@ -1120,34 +1180,34 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C19" t="str">
-        <v>진공단열재</v>
+        <v>시멘트모르타르</v>
       </c>
       <c r="D19" t="str">
-        <v>vacuum_insulation_panel</v>
+        <v>cement_mortar</v>
       </c>
       <c r="E19" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F19" t="str">
-        <v>단열재</v>
+        <v>구조재</v>
       </c>
       <c r="G19">
-        <v>683.98</v>
+        <v>422.11</v>
       </c>
       <c r="H19" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L19" t="str">
-        <v>환경성적표지(주식회사 그린인슐레이터)</v>
+        <v>국내EPD</v>
       </c>
       <c r="N19" t="str">
-        <v>진공단열재(SUPERVAC)</v>
+        <v>((주)삼표산업) 건조시멘트모르타르(일반바닥용) (외 1개 평균)</v>
       </c>
     </row>
     <row r="20">
@@ -1158,10 +1218,10 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C20" t="str">
-        <v>카펫타일</v>
+        <v>액체방수</v>
       </c>
       <c r="D20" t="str">
-        <v>carpet_tile</v>
+        <v>liquid_waterproofing</v>
       </c>
       <c r="E20" t="str">
         <v>finishing</v>
@@ -1170,22 +1230,22 @@
         <v>마감재</v>
       </c>
       <c r="G20">
-        <v>543.1</v>
+        <v>422.11</v>
       </c>
       <c r="H20" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I20">
-        <v>370</v>
+        <v>1800</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L20" t="str">
         <v>국내EPD</v>
       </c>
       <c r="N20" t="str">
-        <v>INFINI COLORS - tufted carpet tiles</v>
+        <v>((주)삼표산업)건조시멘트모르타르(일반바닥용) (외 1개 평균)</v>
       </c>
     </row>
     <row r="21">
@@ -1196,34 +1256,34 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C21" t="str">
-        <v>시멘트모르타르</v>
+        <v>압출법보온판</v>
       </c>
       <c r="D21" t="str">
-        <v>cement_mortar</v>
+        <v>xps</v>
       </c>
       <c r="E21" t="str">
-        <v>finishing</v>
+        <v>insulation</v>
       </c>
       <c r="F21" t="str">
-        <v>구조재</v>
+        <v>단열재</v>
       </c>
       <c r="G21">
-        <v>422.11</v>
+        <v>417.81</v>
       </c>
       <c r="H21" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I21">
-        <v>1800</v>
+        <v>35</v>
       </c>
       <c r="J21">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="L21" t="str">
         <v>국내EPD</v>
       </c>
       <c r="N21" t="str">
-        <v>((주)삼표산업) 건조시멘트모르타르(일반바닥용) (외 1개 평균)</v>
+        <v>2개 제품 평균</v>
       </c>
     </row>
     <row r="22">
@@ -1234,34 +1294,34 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C22" t="str">
-        <v>액체방수</v>
+        <v>콘크리트</v>
       </c>
       <c r="D22" t="str">
-        <v>liquid_waterproofing</v>
+        <v>concrete</v>
       </c>
       <c r="E22" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F22" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G22">
-        <v>422.11</v>
+        <v>345</v>
       </c>
       <c r="H22" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I22">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="L22" t="str">
-        <v>국내EPD</v>
+        <v>국가 LCI DB</v>
       </c>
       <c r="N22" t="str">
-        <v>((주)삼표산업)건조시멘트모르타르(일반바닥용) (외 1개 평균)</v>
+        <v>레디믹스트 콘크리트[25-24-150] (외 1개 평균)</v>
       </c>
     </row>
     <row r="23">
@@ -1272,34 +1332,34 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C23" t="str">
-        <v>압출법보온판</v>
+        <v>대리석</v>
       </c>
       <c r="D23" t="str">
-        <v>xps</v>
+        <v>marble</v>
       </c>
       <c r="E23" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F23" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G23">
-        <v>417.81</v>
+        <v>284</v>
       </c>
       <c r="H23" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I23">
-        <v>35</v>
+        <v>2700</v>
       </c>
       <c r="J23">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="L23" t="str">
-        <v>국내EPD</v>
+        <v>EC3</v>
       </c>
       <c r="N23" t="str">
-        <v>2개 제품 평균</v>
+        <v>5.68 ÷ 0.02 = 284</v>
       </c>
     </row>
     <row r="24">
@@ -1310,10 +1370,10 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C24" t="str">
-        <v>콘크리트</v>
+        <v>저탄소 콘크리트</v>
       </c>
       <c r="D24" t="str">
-        <v>concrete</v>
+        <v>low_carbon_concrete</v>
       </c>
       <c r="E24" t="str">
         <v>structural</v>
@@ -1322,7 +1382,7 @@
         <v>구조재</v>
       </c>
       <c r="G24">
-        <v>345</v>
+        <v>176</v>
       </c>
       <c r="H24" t="str">
         <v>kgCO2e/m³</v>
@@ -1334,10 +1394,10 @@
         <v>150</v>
       </c>
       <c r="L24" t="str">
-        <v>국가 LCI DB</v>
+        <v>국내EPD</v>
       </c>
       <c r="N24" t="str">
-        <v>레디믹스트 콘크리트[25-24-150] (외 1개 평균)</v>
+        <v>한라엔컴(ENCOM)㈜ 레디믹스트 콘크리트[25-24(80, 120, 150, 180, 500),경상도]</v>
       </c>
     </row>
     <row r="25">
@@ -1348,34 +1408,34 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C25" t="str">
-        <v>대리석</v>
+        <v>경질우레탄폼</v>
       </c>
       <c r="D25" t="str">
-        <v>marble</v>
+        <v>rigid_urethane_foam</v>
       </c>
       <c r="E25" t="str">
-        <v>finishing</v>
+        <v>insulation</v>
       </c>
       <c r="F25" t="str">
-        <v>마감재</v>
+        <v>단열재</v>
       </c>
       <c r="G25">
-        <v>284</v>
+        <v>173.96</v>
       </c>
       <c r="H25" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I25">
-        <v>2700</v>
+        <v>35</v>
       </c>
       <c r="J25">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="L25" t="str">
-        <v>EC3</v>
+        <v>국내EPD</v>
       </c>
       <c r="N25" t="str">
-        <v>5.68 ÷ 0.02 = 284</v>
+        <v>8개 제품 평균</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1446,34 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C26" t="str">
-        <v>저탄소 콘크리트</v>
+        <v>합성목재데크</v>
       </c>
       <c r="D26" t="str">
-        <v>low_carbon_concrete</v>
+        <v>composite_wood_deck</v>
       </c>
       <c r="E26" t="str">
-        <v>structural</v>
+        <v>finishing</v>
       </c>
       <c r="F26" t="str">
-        <v>구조재</v>
+        <v>마감재</v>
       </c>
       <c r="G26">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="H26" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I26">
-        <v>2300</v>
+        <v>612</v>
       </c>
       <c r="J26">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="L26" t="str">
-        <v>국내EPD</v>
+        <v>ICE v3</v>
       </c>
       <c r="N26" t="str">
-        <v>한라엔컴(ENCOM)㈜ 레디믹스트 콘크리트[25-24(80, 120, 150, 180, 500),경상도]</v>
+        <v>0.15 × 2600 = 390</v>
       </c>
     </row>
     <row r="27">
@@ -1424,34 +1484,34 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C27" t="str">
-        <v>경질우레탄폼</v>
+        <v>세라믹타일</v>
       </c>
       <c r="D27" t="str">
-        <v>rigid_urethane_foam</v>
+        <v>ceramic_tile</v>
       </c>
       <c r="E27" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F27" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G27">
-        <v>173.96</v>
+        <v>882.5</v>
       </c>
       <c r="H27" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I27">
-        <v>35</v>
+        <v>2500</v>
       </c>
       <c r="J27">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="L27" t="str">
-        <v>국내EPD</v>
+        <v>국가 LCI DB</v>
       </c>
       <c r="N27" t="str">
-        <v>8개 제품 평균</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="28">
@@ -1462,10 +1522,10 @@
         <v>Level 3 (≥100)</v>
       </c>
       <c r="C28" t="str">
-        <v>합성목재데크</v>
+        <v>화강석</v>
       </c>
       <c r="D28" t="str">
-        <v>composite_wood_deck</v>
+        <v>granite</v>
       </c>
       <c r="E28" t="str">
         <v>finishing</v>
@@ -1474,22 +1534,19 @@
         <v>마감재</v>
       </c>
       <c r="G28">
-        <v>150</v>
+        <v>101.76</v>
       </c>
       <c r="H28" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I28">
-        <v>612</v>
+        <v>2650</v>
       </c>
       <c r="J28">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L28" t="str">
-        <v>ICE v3</v>
-      </c>
-      <c r="N28" t="str">
-        <v>0.15 × 2600 = 390</v>
+        <v>국가 LCI DB</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1554,37 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Level 3 (≥100)</v>
+        <v>Level 4 (≥0)</v>
       </c>
       <c r="C29" t="str">
-        <v>세라믹타일</v>
+        <v>PF보드</v>
       </c>
       <c r="D29" t="str">
-        <v>ceramic_tile</v>
+        <v>phenolic_foam_board</v>
       </c>
       <c r="E29" t="str">
-        <v>finishing</v>
+        <v>insulation</v>
       </c>
       <c r="F29" t="str">
-        <v>마감재</v>
+        <v>단열재</v>
       </c>
       <c r="G29">
-        <v>882.5</v>
+        <v>78.21</v>
       </c>
       <c r="H29" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I29">
-        <v>2500</v>
+        <v>33</v>
       </c>
       <c r="J29">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="L29" t="str">
-        <v>국가 LCI DB</v>
+        <v>국내EPD</v>
       </c>
       <c r="N29" t="str">
-        <v xml:space="preserve"> </v>
+        <v>LX Z:IN PF Board/kg</v>
       </c>
     </row>
     <row r="30">
@@ -1535,34 +1592,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Level 3 (≥100)</v>
+        <v>Level 4 (≥0)</v>
       </c>
       <c r="C30" t="str">
-        <v>화강석</v>
+        <v>퍼라이트</v>
       </c>
       <c r="D30" t="str">
-        <v>granite</v>
+        <v>perlite</v>
       </c>
       <c r="E30" t="str">
-        <v>finishing</v>
+        <v>insulation</v>
       </c>
       <c r="F30" t="str">
-        <v>마감재</v>
+        <v>단열재</v>
       </c>
       <c r="G30">
-        <v>101.76</v>
+        <v>75</v>
       </c>
       <c r="H30" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I30">
-        <v>2650</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L30" t="str">
-        <v>국가 LCI DB</v>
+        <v>ICE v3</v>
+      </c>
+      <c r="N30" t="str">
+        <v>0.75 × 100 = 75</v>
       </c>
     </row>
     <row r="31">
@@ -1570,7 +1630,37 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Level 3 (≥100)</v>
+        <v>Level 4 (≥0)</v>
+      </c>
+      <c r="C31" t="str">
+        <v>비드법보온판</v>
+      </c>
+      <c r="D31" t="str">
+        <v>eps</v>
+      </c>
+      <c r="E31" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F31" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G31">
+        <v>58.8</v>
+      </c>
+      <c r="H31" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I31">
+        <v>30</v>
+      </c>
+      <c r="J31">
+        <v>250</v>
+      </c>
+      <c r="L31" t="str">
+        <v>국가 LCI DB</v>
+      </c>
+      <c r="N31" t="str">
+        <v>국가LCIDB</v>
       </c>
     </row>
     <row r="32">
@@ -1578,7 +1668,34 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Level 3 (≥100)</v>
+        <v>Level 4 (≥0)</v>
+      </c>
+      <c r="C32" t="str">
+        <v>암면</v>
+      </c>
+      <c r="D32" t="str">
+        <v>rock_wool</v>
+      </c>
+      <c r="E32" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F32" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G32">
+        <v>51</v>
+      </c>
+      <c r="H32" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I32">
+        <v>50</v>
+      </c>
+      <c r="J32">
+        <v>250</v>
+      </c>
+      <c r="L32" t="str">
+        <v>ICE v3</v>
       </c>
     </row>
     <row r="33">
@@ -1588,6 +1705,33 @@
       <c r="B33" t="str">
         <v>Level 4 (≥0)</v>
       </c>
+      <c r="C33" t="str">
+        <v>그라스울보온판</v>
+      </c>
+      <c r="D33" t="str">
+        <v>glass_wool_board</v>
+      </c>
+      <c r="E33" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F33" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G33">
+        <v>50.4</v>
+      </c>
+      <c r="H33" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I33">
+        <v>48</v>
+      </c>
+      <c r="J33">
+        <v>250</v>
+      </c>
+      <c r="L33" t="str">
+        <v>국가 LCI DB</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1596,6 +1740,36 @@
       <c r="B34" t="str">
         <v>Level 4 (≥0)</v>
       </c>
+      <c r="C34" t="str">
+        <v>대나무구조재</v>
+      </c>
+      <c r="D34" t="str">
+        <v>bamboo_structural</v>
+      </c>
+      <c r="E34" t="str">
+        <v>structural</v>
+      </c>
+      <c r="F34" t="str">
+        <v>구조재</v>
+      </c>
+      <c r="G34">
+        <v>0.2826</v>
+      </c>
+      <c r="H34" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I34">
+        <v>600</v>
+      </c>
+      <c r="J34">
+        <v>200</v>
+      </c>
+      <c r="L34" t="str">
+        <v>2050materials</v>
+      </c>
+      <c r="N34" t="str">
+        <v>bamcore</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1605,34 +1779,34 @@
         <v>Level 4 (≥0)</v>
       </c>
       <c r="C35" t="str">
-        <v>PF보드</v>
+        <v>재활용골재콘크리트</v>
       </c>
       <c r="D35" t="str">
-        <v>phenolic_foam_board</v>
+        <v>recycled_aggregate_concrete</v>
       </c>
       <c r="E35" t="str">
-        <v>insulation</v>
+        <v>structural</v>
       </c>
       <c r="F35" t="str">
-        <v>단열재</v>
+        <v>구조재</v>
       </c>
       <c r="G35">
-        <v>78.21</v>
+        <v>3.96</v>
       </c>
       <c r="H35" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I35">
-        <v>33</v>
+        <v>2200</v>
       </c>
       <c r="J35">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L35" t="str">
-        <v>국내EPD</v>
+        <v>EC3</v>
       </c>
       <c r="N35" t="str">
-        <v>LX Z:IN PF Board/kg</v>
+        <v>CLS6 Recycled Concrete Base</v>
       </c>
     </row>
     <row r="36">
@@ -1640,13 +1814,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
       </c>
       <c r="C36" t="str">
-        <v>퍼라이트</v>
+        <v>양모단열재</v>
       </c>
       <c r="D36" t="str">
-        <v>perlite</v>
+        <v>wool_insulation</v>
       </c>
       <c r="E36" t="str">
         <v>insulation</v>
@@ -1655,22 +1829,22 @@
         <v>단열재</v>
       </c>
       <c r="G36">
-        <v>75</v>
+        <v>-54</v>
       </c>
       <c r="H36" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="J36">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="L36" t="str">
         <v>ICE v3</v>
       </c>
       <c r="N36" t="str">
-        <v>0.75 × 100 = 75</v>
+        <v>-2.16 × 25 = -54</v>
       </c>
     </row>
     <row r="37">
@@ -1678,13 +1852,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
       </c>
       <c r="C37" t="str">
-        <v>비드법보온판</v>
+        <v>셀룰로오스단열재</v>
       </c>
       <c r="D37" t="str">
-        <v>eps</v>
+        <v>cellulose_insulation</v>
       </c>
       <c r="E37" t="str">
         <v>insulation</v>
@@ -1693,22 +1867,22 @@
         <v>단열재</v>
       </c>
       <c r="G37">
-        <v>58.8</v>
+        <v>-61.6</v>
       </c>
       <c r="H37" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I37">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J37">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L37" t="str">
-        <v>국가 LCI DB</v>
+        <v>EC3</v>
       </c>
       <c r="N37" t="str">
-        <v>국가LCIDB</v>
+        <v>Cellulose Insulation</v>
       </c>
     </row>
     <row r="38">
@@ -1716,13 +1890,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
       </c>
       <c r="C38" t="str">
-        <v>암면</v>
+        <v>목섬유단열재</v>
       </c>
       <c r="D38" t="str">
-        <v>rock_wool</v>
+        <v>wood_fiber_insulation</v>
       </c>
       <c r="E38" t="str">
         <v>insulation</v>
@@ -1731,7 +1905,7 @@
         <v>단열재</v>
       </c>
       <c r="G38">
-        <v>51</v>
+        <v>-87</v>
       </c>
       <c r="H38" t="str">
         <v>kgCO2e/m³</v>
@@ -1740,10 +1914,13 @@
         <v>50</v>
       </c>
       <c r="J38">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L38" t="str">
-        <v>ICE v3</v>
+        <v>EC3</v>
+      </c>
+      <c r="N38" t="str">
+        <v>바이오제닉 -1.74 × 50 = -87</v>
       </c>
     </row>
     <row r="39">
@@ -1751,13 +1928,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
       </c>
       <c r="C39" t="str">
-        <v>그라스울보온판</v>
+        <v>헴프단열재</v>
       </c>
       <c r="D39" t="str">
-        <v>glass_wool_board</v>
+        <v>hemp_insulation</v>
       </c>
       <c r="E39" t="str">
         <v>insulation</v>
@@ -1766,19 +1943,22 @@
         <v>단열재</v>
       </c>
       <c r="G39">
-        <v>50.4</v>
+        <v>-87</v>
       </c>
       <c r="H39" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I39">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J39">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L39" t="str">
-        <v>국가 LCI DB</v>
+        <v>EC3</v>
+      </c>
+      <c r="N39" t="str">
+        <v>바이오제닉 -2.175 × 40 = -87</v>
       </c>
     </row>
     <row r="40">
@@ -1786,37 +1966,37 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
       </c>
       <c r="C40" t="str">
-        <v>대나무구조재</v>
+        <v>코르크단열재</v>
       </c>
       <c r="D40" t="str">
-        <v>bamboo_structural</v>
+        <v>cork_insulation</v>
       </c>
       <c r="E40" t="str">
-        <v>structural</v>
+        <v>insulation</v>
       </c>
       <c r="F40" t="str">
-        <v>구조재</v>
+        <v>단열재</v>
       </c>
       <c r="G40">
-        <v>0.2826</v>
+        <v>-130</v>
       </c>
       <c r="H40" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I40">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="J40">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L40" t="str">
-        <v>2050materials</v>
+        <v>ICE v3</v>
       </c>
       <c r="N40" t="str">
-        <v>bamcore</v>
+        <v>바이오제닉 -1.08 × 120 = -130</v>
       </c>
     </row>
     <row r="41">
@@ -1824,37 +2004,37 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
       </c>
       <c r="C41" t="str">
-        <v>재활용골재콘크리트</v>
+        <v>코르크바닥</v>
       </c>
       <c r="D41" t="str">
-        <v>recycled_aggregate_concrete</v>
+        <v>cork_flooring</v>
       </c>
       <c r="E41" t="str">
-        <v>structural</v>
+        <v>finishing</v>
       </c>
       <c r="F41" t="str">
-        <v>구조재</v>
+        <v>마감재</v>
       </c>
       <c r="G41">
-        <v>3.96</v>
+        <v>-195</v>
       </c>
       <c r="H41" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I41">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="J41">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L41" t="str">
-        <v>EC3</v>
+        <v>ICE v3</v>
       </c>
       <c r="N41" t="str">
-        <v>CLS6 Recycled Concrete Base</v>
+        <v>바이오제닉 -0.39 × 500 = -195</v>
       </c>
     </row>
     <row r="42">
@@ -1862,7 +2042,37 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
+      </c>
+      <c r="C42" t="str">
+        <v>볏짚단열패널</v>
+      </c>
+      <c r="D42" t="str">
+        <v>straw_insulation_panel</v>
+      </c>
+      <c r="E42" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F42" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G42">
+        <v>-222</v>
+      </c>
+      <c r="H42" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I42">
+        <v>100</v>
+      </c>
+      <c r="J42">
+        <v>400</v>
+      </c>
+      <c r="L42" t="str">
+        <v xml:space="preserve">EC3 </v>
+      </c>
+      <c r="N42" t="str">
+        <v>(EcoCocon Straw Modules) -</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +2080,37 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
+      </c>
+      <c r="C43" t="str">
+        <v>천연목재데크</v>
+      </c>
+      <c r="D43" t="str">
+        <v>natural_wood_deck</v>
+      </c>
+      <c r="E43" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F43" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G43">
+        <v>-433</v>
+      </c>
+      <c r="H43" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I43">
+        <v>600</v>
+      </c>
+      <c r="J43">
+        <v>25</v>
+      </c>
+      <c r="L43" t="str">
+        <v>2050materials</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Accoya Wood decking</v>
       </c>
     </row>
     <row r="44">
@@ -1878,7 +2118,37 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
+      </c>
+      <c r="C44" t="str">
+        <v>원목마루</v>
+      </c>
+      <c r="D44" t="str">
+        <v>solid_wood_flooring</v>
+      </c>
+      <c r="E44" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F44" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G44">
+        <v>-480</v>
+      </c>
+      <c r="H44" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I44">
+        <v>600</v>
+      </c>
+      <c r="J44">
+        <v>15</v>
+      </c>
+      <c r="L44" t="str">
+        <v>EC3</v>
+      </c>
+      <c r="N44" t="str">
+        <v>바이오제닉 -0.8 × 600 = -480</v>
       </c>
     </row>
     <row r="45">
@@ -1886,7 +2156,34 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
+      </c>
+      <c r="C45" t="str">
+        <v>clt</v>
+      </c>
+      <c r="D45" t="str">
+        <v>clt</v>
+      </c>
+      <c r="E45" t="str">
+        <v>structural</v>
+      </c>
+      <c r="F45" t="str">
+        <v>구조재</v>
+      </c>
+      <c r="G45">
+        <v>-505.4</v>
+      </c>
+      <c r="H45" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I45">
+        <v>430</v>
+      </c>
+      <c r="J45">
+        <v>150</v>
+      </c>
+      <c r="L45" t="str">
+        <v>okobaudat</v>
       </c>
     </row>
     <row r="46">
@@ -1894,7 +2191,37 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
+      </c>
+      <c r="C46" t="str">
+        <v>합판</v>
+      </c>
+      <c r="D46" t="str">
+        <v>plywood</v>
+      </c>
+      <c r="E46" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F46" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G46">
+        <v>-649</v>
+      </c>
+      <c r="H46" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I46">
+        <v>480</v>
+      </c>
+      <c r="J46">
+        <v>12</v>
+      </c>
+      <c r="L46" t="str">
+        <v>EC3</v>
+      </c>
+      <c r="N46" t="str">
+        <v>trae.dk</v>
       </c>
     </row>
     <row r="47">
@@ -1902,7 +2229,43 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
+      </c>
+      <c r="C47" t="str">
+        <v>목재틀</v>
+      </c>
+      <c r="D47" t="str">
+        <v>wood_subframe</v>
+      </c>
+      <c r="E47" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F47" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G47">
+        <v>-693</v>
+      </c>
+      <c r="H47" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I47">
+        <v>450</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47" t="str">
+        <v>○</v>
+      </c>
+      <c r="L47" t="str">
+        <v>2050materials</v>
+      </c>
+      <c r="M47" t="str">
+        <v>40×40mm @ 400mm 간격 (단방향)</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Roseburg, Sofrwood lumber</v>
       </c>
     </row>
     <row r="48">
@@ -1910,733 +2273,229 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Level 4 (≥0)</v>
+        <v>Level 5 (&lt;0)</v>
+      </c>
+      <c r="C48" t="str">
+        <v>강화마루</v>
+      </c>
+      <c r="D48" t="str">
+        <v>laminate_flooring</v>
+      </c>
+      <c r="E48" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F48" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G48">
+        <v>-994</v>
+      </c>
+      <c r="H48" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I48">
+        <v>774</v>
+      </c>
+      <c r="J48">
+        <v>10</v>
+      </c>
+      <c r="L48" t="str">
+        <v>EC3</v>
+      </c>
+      <c r="N48" t="str">
+        <v>mohwk industries</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>Level 4 (≥0)</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>Level 4 (≥0)</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>Level 4 (≥0)</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>Level 4 (≥0)</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>Level 4 (≥0)</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>Level 4 (≥0)</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C56" t="str">
-        <v>양모단열재</v>
-      </c>
-      <c r="D56" t="str">
-        <v>wool_insulation</v>
-      </c>
-      <c r="E56" t="str">
-        <v>insulation</v>
-      </c>
-      <c r="F56" t="str">
-        <v>단열재</v>
-      </c>
-      <c r="G56">
-        <v>-54</v>
-      </c>
-      <c r="H56" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I56">
-        <v>25</v>
-      </c>
-      <c r="J56">
-        <v>300</v>
-      </c>
-      <c r="L56" t="str">
-        <v>ICE v3</v>
-      </c>
-      <c r="N56" t="str">
-        <v>-2.16 × 25 = -54</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C57" t="str">
-        <v>셀룰로오스단열재</v>
-      </c>
-      <c r="D57" t="str">
-        <v>cellulose_insulation</v>
-      </c>
-      <c r="E57" t="str">
-        <v>insulation</v>
-      </c>
-      <c r="F57" t="str">
-        <v>단열재</v>
-      </c>
-      <c r="G57">
-        <v>-61.6</v>
-      </c>
-      <c r="H57" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I57">
-        <v>40</v>
-      </c>
-      <c r="J57">
-        <v>400</v>
-      </c>
-      <c r="L57" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N57" t="str">
-        <v>Cellulose Insulation</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C58" t="str">
-        <v>목섬유단열재</v>
-      </c>
-      <c r="D58" t="str">
-        <v>wood_fiber_insulation</v>
-      </c>
-      <c r="E58" t="str">
-        <v>insulation</v>
-      </c>
-      <c r="F58" t="str">
-        <v>단열재</v>
-      </c>
-      <c r="G58">
-        <v>-87</v>
-      </c>
-      <c r="H58" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I58">
-        <v>50</v>
-      </c>
-      <c r="J58">
-        <v>300</v>
-      </c>
-      <c r="L58" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N58" t="str">
-        <v>바이오제닉 -1.74 × 50 = -87</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C59" t="str">
-        <v>헴프단열재</v>
-      </c>
-      <c r="D59" t="str">
-        <v>hemp_insulation</v>
-      </c>
-      <c r="E59" t="str">
-        <v>insulation</v>
-      </c>
-      <c r="F59" t="str">
-        <v>단열재</v>
-      </c>
-      <c r="G59">
-        <v>-87</v>
-      </c>
-      <c r="H59" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I59">
-        <v>40</v>
-      </c>
-      <c r="J59">
-        <v>300</v>
-      </c>
-      <c r="L59" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N59" t="str">
-        <v>바이오제닉 -2.175 × 40 = -87</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C60" t="str">
-        <v>코르크단열재</v>
-      </c>
-      <c r="D60" t="str">
-        <v>cork_insulation</v>
-      </c>
-      <c r="E60" t="str">
-        <v>insulation</v>
-      </c>
-      <c r="F60" t="str">
-        <v>단열재</v>
-      </c>
-      <c r="G60">
-        <v>-130</v>
-      </c>
-      <c r="H60" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I60">
-        <v>120</v>
-      </c>
-      <c r="J60">
-        <v>300</v>
-      </c>
-      <c r="L60" t="str">
-        <v>ICE v3</v>
-      </c>
-      <c r="N60" t="str">
-        <v>바이오제닉 -1.08 × 120 = -130</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C61" t="str">
-        <v>코르크바닥</v>
-      </c>
-      <c r="D61" t="str">
-        <v>cork_flooring</v>
-      </c>
-      <c r="E61" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F61" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G61">
-        <v>-195</v>
-      </c>
-      <c r="H61" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I61">
-        <v>500</v>
-      </c>
-      <c r="J61">
-        <v>6</v>
-      </c>
-      <c r="L61" t="str">
-        <v>ICE v3</v>
-      </c>
-      <c r="N61" t="str">
-        <v>바이오제닉 -0.39 × 500 = -195</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C62" t="str">
-        <v>볏짚단열패널</v>
-      </c>
-      <c r="D62" t="str">
-        <v>straw_insulation_panel</v>
-      </c>
-      <c r="E62" t="str">
-        <v>insulation</v>
-      </c>
-      <c r="F62" t="str">
-        <v>단열재</v>
-      </c>
-      <c r="G62">
-        <v>-222</v>
-      </c>
-      <c r="H62" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I62">
-        <v>100</v>
-      </c>
-      <c r="J62">
-        <v>400</v>
-      </c>
-      <c r="L62" t="str">
-        <v xml:space="preserve">EC3 </v>
-      </c>
-      <c r="N62" t="str">
-        <v>(EcoCocon Straw Modules) -</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C63" t="str">
-        <v>천연목재데크</v>
-      </c>
-      <c r="D63" t="str">
-        <v>natural_wood_deck</v>
-      </c>
-      <c r="E63" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F63" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G63">
-        <v>-433</v>
-      </c>
-      <c r="H63" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I63">
-        <v>600</v>
-      </c>
-      <c r="J63">
-        <v>25</v>
-      </c>
-      <c r="L63" t="str">
-        <v>2050materials</v>
-      </c>
-      <c r="N63" t="str">
-        <v>Accoya Wood decking</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C64" t="str">
-        <v>원목마루</v>
-      </c>
-      <c r="D64" t="str">
-        <v>solid_wood_flooring</v>
-      </c>
-      <c r="E64" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F64" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G64">
-        <v>-480</v>
-      </c>
-      <c r="H64" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I64">
-        <v>600</v>
-      </c>
-      <c r="J64">
-        <v>15</v>
-      </c>
-      <c r="L64" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N64" t="str">
-        <v>바이오제닉 -0.8 × 600 = -480</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C65" t="str">
-        <v>clt</v>
-      </c>
-      <c r="D65" t="str">
-        <v>clt</v>
-      </c>
-      <c r="E65" t="str">
-        <v>structural</v>
-      </c>
-      <c r="F65" t="str">
-        <v>구조재</v>
-      </c>
-      <c r="G65">
-        <v>-505.4</v>
-      </c>
-      <c r="H65" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I65">
-        <v>430</v>
-      </c>
-      <c r="J65">
-        <v>150</v>
-      </c>
-      <c r="L65" t="str">
-        <v>okobaudat</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C66" t="str">
-        <v>합판</v>
-      </c>
-      <c r="D66" t="str">
-        <v>plywood</v>
-      </c>
-      <c r="E66" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F66" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G66">
-        <v>-649</v>
-      </c>
-      <c r="H66" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I66">
-        <v>480</v>
-      </c>
-      <c r="J66">
-        <v>12</v>
-      </c>
-      <c r="L66" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N66" t="str">
-        <v>trae.dk</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C67" t="str">
-        <v>목재틀</v>
-      </c>
-      <c r="D67" t="str">
-        <v>wood_subframe</v>
-      </c>
-      <c r="E67" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F67" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G67">
-        <v>-693</v>
-      </c>
-      <c r="H67" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I67">
-        <v>450</v>
-      </c>
-      <c r="J67">
-        <v>4</v>
-      </c>
-      <c r="K67" t="str">
-        <v>○</v>
-      </c>
-      <c r="L67" t="str">
-        <v>2050materials</v>
-      </c>
-      <c r="M67" t="str">
-        <v>40×40mm @ 400mm 간격 (단방향)</v>
-      </c>
-      <c r="N67" t="str">
-        <v>Roseburg, Sofrwood lumber</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C68" t="str">
-        <v>강화마루</v>
-      </c>
-      <c r="D68" t="str">
-        <v>laminate_flooring</v>
-      </c>
-      <c r="E68" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F68" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G68">
-        <v>-994</v>
-      </c>
-      <c r="H68" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I68">
-        <v>774</v>
-      </c>
-      <c r="J68">
-        <v>10</v>
-      </c>
-      <c r="L68" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N68" t="str">
-        <v>mohwk industries</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N88"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N84"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3934,6 +3793,36 @@
       <c r="B35">
         <v>3</v>
       </c>
+      <c r="C35" t="str">
+        <v>재활용유리타일</v>
+      </c>
+      <c r="D35" t="str">
+        <v>recycled_glass_tile</v>
+      </c>
+      <c r="E35" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F35" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G35">
+        <v>178</v>
+      </c>
+      <c r="H35" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I35">
+        <v>2500</v>
+      </c>
+      <c r="J35">
+        <v>10</v>
+      </c>
+      <c r="K35" t="str">
+        <v xml:space="preserve">EC3 </v>
+      </c>
+      <c r="M35" t="str">
+        <v>(LAVA Ezarri Recycled Glass) 1.78 kgCO2e/m² ÷ 0.01 = 178 kgCO2e/m³</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -3943,10 +3832,10 @@
         <v>3</v>
       </c>
       <c r="C36" t="str">
-        <v>재활용유리타일</v>
+        <v>유리모자이크타일</v>
       </c>
       <c r="D36" t="str">
-        <v>recycled_glass_tile</v>
+        <v>glass_mosaic_tile</v>
       </c>
       <c r="E36" t="str">
         <v>finishing</v>
@@ -3964,13 +3853,13 @@
         <v>2500</v>
       </c>
       <c r="J36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K36" t="str">
         <v xml:space="preserve">EC3 </v>
       </c>
       <c r="M36" t="str">
-        <v>(LAVA Ezarri Recycled Glass) 1.78 kgCO2e/m² ÷ 0.01 = 178 kgCO2e/m³</v>
+        <v>(VIDREPUR Glass Mosaic)유리 모자이크 ~178 kgCO2e/m³ (EC3)</v>
       </c>
     </row>
     <row r="37">
@@ -3981,34 +3870,34 @@
         <v>3</v>
       </c>
       <c r="C37" t="str">
-        <v>유리모자이크타일</v>
+        <v>저탄소 콘크리트</v>
       </c>
       <c r="D37" t="str">
-        <v>glass_mosaic_tile</v>
+        <v>low_carbon_concrete</v>
       </c>
       <c r="E37" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F37" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G37">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H37" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I37">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="K37" t="str">
-        <v xml:space="preserve">EC3 </v>
+        <v>국내EPD</v>
       </c>
       <c r="M37" t="str">
-        <v>(VIDREPUR Glass Mosaic)유리 모자이크 ~178 kgCO2e/m³ (EC3)</v>
+        <v>한라엔컴(ENCOM)㈜ 레디믹스트 콘크리트[25-24(80, 120, 150, 180, 500),경상도]</v>
       </c>
     </row>
     <row r="38">
@@ -4019,34 +3908,34 @@
         <v>3</v>
       </c>
       <c r="C38" t="str">
-        <v>저탄소 콘크리트</v>
+        <v>경질우레탄폼</v>
       </c>
       <c r="D38" t="str">
-        <v>low_carbon_concrete</v>
+        <v>rigid_urethane_foam</v>
       </c>
       <c r="E38" t="str">
-        <v>structural</v>
+        <v>insulation</v>
       </c>
       <c r="F38" t="str">
-        <v>구조재</v>
+        <v>단열재</v>
       </c>
       <c r="G38">
-        <v>176</v>
+        <v>173.96</v>
       </c>
       <c r="H38" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I38">
-        <v>2300</v>
+        <v>35</v>
       </c>
       <c r="J38">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="K38" t="str">
         <v>국내EPD</v>
       </c>
       <c r="M38" t="str">
-        <v>한라엔컴(ENCOM)㈜ 레디믹스트 콘크리트[25-24(80, 120, 150, 180, 500),경상도]</v>
+        <v>8개 제품 평균</v>
       </c>
     </row>
     <row r="39">
@@ -4057,34 +3946,34 @@
         <v>3</v>
       </c>
       <c r="C39" t="str">
-        <v>경질우레탄폼</v>
+        <v>점토미장</v>
       </c>
       <c r="D39" t="str">
-        <v>rigid_urethane_foam</v>
+        <v>clay_plaster</v>
       </c>
       <c r="E39" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F39" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G39">
-        <v>173.96</v>
+        <v>154</v>
       </c>
       <c r="H39" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I39">
-        <v>35</v>
+        <v>1600</v>
       </c>
       <c r="J39">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K39" t="str">
-        <v>국내EPD</v>
+        <v xml:space="preserve">EC3 </v>
       </c>
       <c r="M39" t="str">
-        <v>8개 제품 평균</v>
+        <v>(Tonalclay Plaster) 0.0768 kgCO2e/kg × 2000 kg/m³ = 154 kgCO2e/m³</v>
       </c>
     </row>
     <row r="40">
@@ -4095,10 +3984,10 @@
         <v>3</v>
       </c>
       <c r="C40" t="str">
-        <v>점토미장</v>
+        <v>샌드스톤</v>
       </c>
       <c r="D40" t="str">
-        <v>clay_plaster</v>
+        <v>sandstone</v>
       </c>
       <c r="E40" t="str">
         <v>finishing</v>
@@ -4107,22 +3996,19 @@
         <v>마감재</v>
       </c>
       <c r="G40">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="H40" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I40">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="J40">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K40" t="str">
-        <v xml:space="preserve">EC3 </v>
-      </c>
-      <c r="M40" t="str">
-        <v>(Tonalclay Plaster) 0.0768 kgCO2e/kg × 2000 kg/m³ = 154 kgCO2e/m³</v>
+        <v>ICE v3</v>
       </c>
     </row>
     <row r="41">
@@ -4133,10 +4019,10 @@
         <v>3</v>
       </c>
       <c r="C41" t="str">
-        <v>샌드스톤</v>
+        <v>화강석</v>
       </c>
       <c r="D41" t="str">
-        <v>sandstone</v>
+        <v>granite</v>
       </c>
       <c r="E41" t="str">
         <v>finishing</v>
@@ -4145,19 +4031,19 @@
         <v>마감재</v>
       </c>
       <c r="G41">
-        <v>125</v>
+        <v>101.76</v>
       </c>
       <c r="H41" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I41">
-        <v>2300</v>
+        <v>2650</v>
       </c>
       <c r="J41">
         <v>30</v>
       </c>
       <c r="K41" t="str">
-        <v>ICE v3</v>
+        <v>국가 LCI DB</v>
       </c>
     </row>
     <row r="42">
@@ -4165,13 +4051,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42" t="str">
-        <v>화강석</v>
+        <v>라임스톤</v>
       </c>
       <c r="D42" t="str">
-        <v>granite</v>
+        <v>limestone</v>
       </c>
       <c r="E42" t="str">
         <v>finishing</v>
@@ -4180,19 +4066,19 @@
         <v>마감재</v>
       </c>
       <c r="G42">
-        <v>101.76</v>
+        <v>90</v>
       </c>
       <c r="H42" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I42">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="J42">
         <v>30</v>
       </c>
       <c r="K42" t="str">
-        <v>국가 LCI DB</v>
+        <v>ICE v3</v>
       </c>
     </row>
     <row r="43">
@@ -4203,31 +4089,34 @@
         <v>4</v>
       </c>
       <c r="C43" t="str">
-        <v>라임스톤</v>
+        <v>PF보드</v>
       </c>
       <c r="D43" t="str">
-        <v>limestone</v>
+        <v>phenolic_foam_board</v>
       </c>
       <c r="E43" t="str">
-        <v>finishing</v>
+        <v>insulation</v>
       </c>
       <c r="F43" t="str">
-        <v>마감재</v>
+        <v>단열재</v>
       </c>
       <c r="G43">
+        <v>78.21</v>
+      </c>
+      <c r="H43" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I43">
+        <v>33</v>
+      </c>
+      <c r="J43">
         <v>90</v>
       </c>
-      <c r="H43" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I43">
-        <v>2500</v>
-      </c>
-      <c r="J43">
-        <v>30</v>
-      </c>
       <c r="K43" t="str">
-        <v>ICE v3</v>
+        <v>국내EPD</v>
+      </c>
+      <c r="M43" t="str">
+        <v>LX Z:IN PF Board/kg</v>
       </c>
     </row>
     <row r="44">
@@ -4238,10 +4127,10 @@
         <v>4</v>
       </c>
       <c r="C44" t="str">
-        <v>PF보드</v>
+        <v>비드법보온판</v>
       </c>
       <c r="D44" t="str">
-        <v>phenolic_foam_board</v>
+        <v>eps</v>
       </c>
       <c r="E44" t="str">
         <v>insulation</v>
@@ -4250,22 +4139,22 @@
         <v>단열재</v>
       </c>
       <c r="G44">
-        <v>78.21</v>
+        <v>58.8</v>
       </c>
       <c r="H44" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I44">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J44">
         <v>90</v>
       </c>
       <c r="K44" t="str">
-        <v>국내EPD</v>
+        <v>국가 LCI DB</v>
       </c>
       <c r="M44" t="str">
-        <v>LX Z:IN PF Board/kg</v>
+        <v>국가LCIDB</v>
       </c>
     </row>
     <row r="45">
@@ -4276,10 +4165,10 @@
         <v>4</v>
       </c>
       <c r="C45" t="str">
-        <v>비드법보온판</v>
+        <v>그라스울보온판</v>
       </c>
       <c r="D45" t="str">
-        <v>eps</v>
+        <v>glass_wool_board</v>
       </c>
       <c r="E45" t="str">
         <v>insulation</v>
@@ -4288,22 +4177,19 @@
         <v>단열재</v>
       </c>
       <c r="G45">
-        <v>58.8</v>
+        <v>50.4</v>
       </c>
       <c r="H45" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I45">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="J45">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="K45" t="str">
         <v>국가 LCI DB</v>
-      </c>
-      <c r="M45" t="str">
-        <v>국가LCIDB</v>
       </c>
     </row>
     <row r="46">
@@ -4314,31 +4200,31 @@
         <v>4</v>
       </c>
       <c r="C46" t="str">
-        <v>그라스울보온판</v>
+        <v>재사용벽돌</v>
       </c>
       <c r="D46" t="str">
-        <v>glass_wool_board</v>
+        <v>reclaimed_brick</v>
       </c>
       <c r="E46" t="str">
-        <v>insulation</v>
+        <v>structural</v>
       </c>
       <c r="F46" t="str">
-        <v>단열재</v>
+        <v>구조재</v>
       </c>
       <c r="G46">
-        <v>50.4</v>
+        <v>39.9</v>
       </c>
       <c r="H46" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I46">
-        <v>48</v>
+        <v>1801</v>
       </c>
       <c r="J46">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="K46" t="str">
-        <v>국가 LCI DB</v>
+        <v>au</v>
       </c>
     </row>
     <row r="47">
@@ -4349,10 +4235,10 @@
         <v>4</v>
       </c>
       <c r="C47" t="str">
-        <v>재사용벽돌</v>
+        <v>흙벽돌</v>
       </c>
       <c r="D47" t="str">
-        <v>reclaimed_brick</v>
+        <v>adobe_brick</v>
       </c>
       <c r="E47" t="str">
         <v>structural</v>
@@ -4361,19 +4247,22 @@
         <v>구조재</v>
       </c>
       <c r="G47">
-        <v>39.9</v>
+        <v>9.96099592</v>
       </c>
       <c r="H47" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I47">
-        <v>1801</v>
+        <v>2000</v>
       </c>
       <c r="J47">
-        <v>57</v>
+        <v>190</v>
       </c>
       <c r="K47" t="str">
-        <v>au</v>
+        <v>okobaudat</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Mineral building products' / 'Bricks  blocks and elements' / 'Air-dried brick (adobe)'</v>
       </c>
     </row>
     <row r="48">
@@ -4384,10 +4273,10 @@
         <v>4</v>
       </c>
       <c r="C48" t="str">
-        <v>흙벽돌</v>
+        <v>재활용골재콘크리트</v>
       </c>
       <c r="D48" t="str">
-        <v>adobe_brick</v>
+        <v>recycled_aggregate_concrete</v>
       </c>
       <c r="E48" t="str">
         <v>structural</v>
@@ -4396,22 +4285,22 @@
         <v>구조재</v>
       </c>
       <c r="G48">
-        <v>9.96099592</v>
+        <v>3.96</v>
       </c>
       <c r="H48" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I48">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="J48">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="K48" t="str">
-        <v>okobaudat</v>
+        <v>EC3</v>
       </c>
       <c r="M48" t="str">
-        <v>Mineral building products' / 'Bricks  blocks and elements' / 'Air-dried brick (adobe)'</v>
+        <v>CLS6 Recycled Concrete Base</v>
       </c>
     </row>
     <row r="49">
@@ -4422,10 +4311,10 @@
         <v>4</v>
       </c>
       <c r="C49" t="str">
-        <v>재활용골재콘크리트</v>
+        <v>대나무구조재</v>
       </c>
       <c r="D49" t="str">
-        <v>recycled_aggregate_concrete</v>
+        <v>bamboo_structural</v>
       </c>
       <c r="E49" t="str">
         <v>structural</v>
@@ -4434,22 +4323,22 @@
         <v>구조재</v>
       </c>
       <c r="G49">
-        <v>3.96</v>
+        <v>0.2826</v>
       </c>
       <c r="H49" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I49">
-        <v>2200</v>
+        <v>600</v>
       </c>
       <c r="J49">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K49" t="str">
-        <v>EC3</v>
+        <v>2050materials</v>
       </c>
       <c r="M49" t="str">
-        <v>CLS6 Recycled Concrete Base</v>
+        <v>bamcore</v>
       </c>
     </row>
     <row r="50">
@@ -4457,13 +4346,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C50" t="str">
-        <v>대나무구조재</v>
+        <v>대마콘크리트블럭</v>
       </c>
       <c r="D50" t="str">
-        <v>bamboo_structural</v>
+        <v>hempcrete</v>
       </c>
       <c r="E50" t="str">
         <v>structural</v>
@@ -4472,22 +4361,22 @@
         <v>구조재</v>
       </c>
       <c r="G50">
-        <v>0.2826</v>
+        <v>-1.94</v>
       </c>
       <c r="H50" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I50">
-        <v>600</v>
+        <v>330</v>
       </c>
       <c r="J50">
         <v>200</v>
       </c>
       <c r="K50" t="str">
-        <v>2050materials</v>
+        <v>EC3</v>
       </c>
       <c r="M50" t="str">
-        <v>bamcore</v>
+        <v>ISOHEMP</v>
       </c>
     </row>
     <row r="51">
@@ -4498,34 +4387,34 @@
         <v>5</v>
       </c>
       <c r="C51" t="str">
-        <v>대마콘크리트블럭</v>
+        <v>양모단열재</v>
       </c>
       <c r="D51" t="str">
-        <v>hempcrete</v>
+        <v>wool_insulation</v>
       </c>
       <c r="E51" t="str">
-        <v>structural</v>
+        <v>insulation</v>
       </c>
       <c r="F51" t="str">
-        <v>구조재</v>
+        <v>단열재</v>
       </c>
       <c r="G51">
-        <v>-1.94</v>
+        <v>-54</v>
       </c>
       <c r="H51" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I51">
-        <v>330</v>
+        <v>25</v>
       </c>
       <c r="J51">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="K51" t="str">
-        <v>EC3</v>
+        <v>ICE v3</v>
       </c>
       <c r="M51" t="str">
-        <v>ISOHEMP</v>
+        <v>-2.16 × 25 = -54</v>
       </c>
     </row>
     <row r="52">
@@ -4536,10 +4425,10 @@
         <v>5</v>
       </c>
       <c r="C52" t="str">
-        <v>양모단열재</v>
+        <v>셀룰로오스단열재</v>
       </c>
       <c r="D52" t="str">
-        <v>wool_insulation</v>
+        <v>cellulose_insulation</v>
       </c>
       <c r="E52" t="str">
         <v>insulation</v>
@@ -4548,22 +4437,22 @@
         <v>단열재</v>
       </c>
       <c r="G52">
-        <v>-54</v>
+        <v>-61.6</v>
       </c>
       <c r="H52" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I52">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J52">
         <v>130</v>
       </c>
       <c r="K52" t="str">
-        <v>ICE v3</v>
+        <v>EC3</v>
       </c>
       <c r="M52" t="str">
-        <v>-2.16 × 25 = -54</v>
+        <v>Cellulose Insulation</v>
       </c>
     </row>
     <row r="53">
@@ -4574,10 +4463,10 @@
         <v>5</v>
       </c>
       <c r="C53" t="str">
-        <v>셀룰로오스단열재</v>
+        <v>헴프단열재</v>
       </c>
       <c r="D53" t="str">
-        <v>cellulose_insulation</v>
+        <v>hemp_insulation</v>
       </c>
       <c r="E53" t="str">
         <v>insulation</v>
@@ -4586,7 +4475,7 @@
         <v>단열재</v>
       </c>
       <c r="G53">
-        <v>-61.6</v>
+        <v>-87</v>
       </c>
       <c r="H53" t="str">
         <v>kgCO2e/m³</v>
@@ -4601,7 +4490,7 @@
         <v>EC3</v>
       </c>
       <c r="M53" t="str">
-        <v>Cellulose Insulation</v>
+        <v>바이오제닉 -2.175 × 40 = -87</v>
       </c>
     </row>
     <row r="54">
@@ -4612,10 +4501,10 @@
         <v>5</v>
       </c>
       <c r="C54" t="str">
-        <v>헴프단열재</v>
+        <v>목섬유단열재</v>
       </c>
       <c r="D54" t="str">
-        <v>hemp_insulation</v>
+        <v>wood_fiber_insulation</v>
       </c>
       <c r="E54" t="str">
         <v>insulation</v>
@@ -4630,16 +4519,16 @@
         <v>kgCO2e/m³</v>
       </c>
       <c r="I54">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J54">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="K54" t="str">
         <v>EC3</v>
       </c>
       <c r="M54" t="str">
-        <v>바이오제닉 -2.175 × 40 = -87</v>
+        <v>바이오제닉 -1.74 × 50 = -87</v>
       </c>
     </row>
     <row r="55">
@@ -4650,10 +4539,10 @@
         <v>5</v>
       </c>
       <c r="C55" t="str">
-        <v>목섬유단열재</v>
+        <v>코르크단열재</v>
       </c>
       <c r="D55" t="str">
-        <v>wood_fiber_insulation</v>
+        <v>cork_insulation</v>
       </c>
       <c r="E55" t="str">
         <v>insulation</v>
@@ -4662,226 +4551,226 @@
         <v>단열재</v>
       </c>
       <c r="G55">
-        <v>-87</v>
+        <v>-130</v>
       </c>
       <c r="H55" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I55">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="J55">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="K55" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="M55" t="str">
-        <v>바이오제닉 -1.74 × 50 = -87</v>
+        <v>ICE v3</v>
+      </c>
+      <c r="L55" t="str">
+        <v>바이오제닉 -1.08 × 120 = -130</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56">
         <v>5</v>
       </c>
       <c r="C56" t="str">
-        <v>코르크단열재</v>
+        <v>코르크패널</v>
       </c>
       <c r="D56" t="str">
-        <v>cork_insulation</v>
+        <v>cork_flooring</v>
       </c>
       <c r="E56" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F56" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G56">
-        <v>-130</v>
+        <v>-195</v>
       </c>
       <c r="H56" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I56">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="J56">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="K56" t="str">
         <v>ICE v3</v>
       </c>
-      <c r="L56" t="str">
-        <v>바이오제닉 -1.08 × 120 = -130</v>
+      <c r="M56" t="str">
+        <v>바이오제닉 -0.39 × 500 = -195</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57">
         <v>5</v>
       </c>
       <c r="C57" t="str">
-        <v>코르크패널</v>
+        <v>볏짚단열패널</v>
       </c>
       <c r="D57" t="str">
-        <v>cork_flooring</v>
+        <v>straw_insulation_panel</v>
       </c>
       <c r="E57" t="str">
-        <v>finishing</v>
+        <v>insulation</v>
       </c>
       <c r="F57" t="str">
-        <v>마감재</v>
+        <v>단열재</v>
       </c>
       <c r="G57">
-        <v>-195</v>
+        <v>-222</v>
       </c>
       <c r="H57" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I57">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="K57" t="str">
-        <v>ICE v3</v>
+        <v xml:space="preserve">EC3 </v>
       </c>
       <c r="M57" t="str">
-        <v>바이오제닉 -0.39 × 500 = -195</v>
+        <v>(EcoCocon Straw Modules) -</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58">
         <v>5</v>
       </c>
       <c r="C58" t="str">
-        <v>볏짚단열패널</v>
+        <v>목재사이딩</v>
       </c>
       <c r="D58" t="str">
-        <v>straw_insulation_panel</v>
+        <v>wood_siding</v>
       </c>
       <c r="E58" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F58" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G58">
-        <v>-222</v>
+        <v>-480</v>
       </c>
       <c r="H58" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I58">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J58">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="K58" t="str">
-        <v xml:space="preserve">EC3 </v>
+        <v>EC3</v>
       </c>
       <c r="M58" t="str">
-        <v>(EcoCocon Straw Modules) -</v>
+        <v>바이오제닉 -0.96 × 500 = -480</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59">
         <v>5</v>
       </c>
       <c r="C59" t="str">
-        <v>목재사이딩</v>
+        <v>clt</v>
       </c>
       <c r="D59" t="str">
-        <v>wood_siding</v>
+        <v>clt</v>
       </c>
       <c r="E59" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F59" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G59">
-        <v>-480</v>
+        <v>-505.4</v>
       </c>
       <c r="H59" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I59">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="J59">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="K59" t="str">
-        <v>EC3</v>
+        <v>okobaudat</v>
       </c>
       <c r="M59" t="str">
-        <v>바이오제닉 -0.96 × 500 = -480</v>
+        <v>집성목 -650</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60">
         <v>5</v>
       </c>
       <c r="C60" t="str">
-        <v>clt</v>
+        <v>합판</v>
       </c>
       <c r="D60" t="str">
-        <v>clt</v>
+        <v>plywood</v>
       </c>
       <c r="E60" t="str">
-        <v>structural</v>
+        <v>finishing</v>
       </c>
       <c r="F60" t="str">
-        <v>구조재</v>
+        <v>마감재</v>
       </c>
       <c r="G60">
-        <v>-505.4</v>
+        <v>-649</v>
       </c>
       <c r="H60" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I60">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="J60">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="K60" t="str">
-        <v>okobaudat</v>
+        <v>EC3</v>
       </c>
       <c r="M60" t="str">
-        <v>집성목 -650</v>
+        <v>trae.dk</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61">
         <v>5</v>
       </c>
       <c r="C61" t="str">
-        <v>합판</v>
+        <v>목재틀</v>
       </c>
       <c r="D61" t="str">
-        <v>plywood</v>
+        <v>wood_subframe</v>
       </c>
       <c r="E61" t="str">
         <v>finishing</v>
@@ -4890,116 +4779,188 @@
         <v>마감재</v>
       </c>
       <c r="G61">
-        <v>-649</v>
+        <v>-693</v>
       </c>
       <c r="H61" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I61">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="J61">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K61" t="str">
-        <v>EC3</v>
+        <v>2050materials</v>
+      </c>
+      <c r="L61" t="str">
+        <v>40×40mm @ 400mm 간격 (단방향)</v>
       </c>
       <c r="M61" t="str">
-        <v>trae.dk</v>
+        <v>Roseburg, Sofrwood lumber</v>
+      </c>
+      <c r="N61" t="str">
+        <v>○</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62">
         <v>5</v>
       </c>
       <c r="C62" t="str">
-        <v>목재틀</v>
+        <v>OSB</v>
       </c>
       <c r="D62" t="str">
-        <v>wood_subframe</v>
+        <v>osb</v>
       </c>
       <c r="E62" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F62" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G62">
-        <v>-693</v>
+        <v>-1220</v>
       </c>
       <c r="H62" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I62">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K62" t="str">
-        <v>2050materials</v>
-      </c>
-      <c r="L62" t="str">
-        <v>40×40mm @ 400mm 간격 (단방향)</v>
+        <v>okobaudat</v>
       </c>
       <c r="M62" t="str">
-        <v>Roseburg, Sofrwood lumber</v>
-      </c>
-      <c r="N62" t="str">
-        <v>○</v>
+        <v xml:space="preserve">Oriented Strand Board / EGGER  </v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
         <v>63</v>
       </c>
-      <c r="B63">
-        <v>5</v>
-      </c>
-      <c r="C63" t="str">
-        <v>OSB</v>
-      </c>
-      <c r="D63" t="str">
-        <v>osb</v>
-      </c>
-      <c r="E63" t="str">
-        <v>structural</v>
-      </c>
-      <c r="F63" t="str">
-        <v>구조재</v>
-      </c>
-      <c r="G63">
-        <v>-1220</v>
-      </c>
-      <c r="H63" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I63">
-        <v>630</v>
-      </c>
-      <c r="J63">
-        <v>16</v>
-      </c>
-      <c r="K63" t="str">
-        <v>okobaudat</v>
-      </c>
-      <c r="M63" t="str">
-        <v xml:space="preserve">Oriented Strand Board / EGGER  </v>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N84"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5049,8 +5010,8 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Level 1 (≥10000)</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
         <v>스테인리스스틸</v>
@@ -5090,8 +5051,8 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Level 1 (≥10000)</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v>구리판</v>
@@ -5131,8 +5092,8 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Level 1 (≥10000)</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>용융아연도금철판</v>
@@ -5169,8 +5130,8 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Level 1 (≥10000)</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v>스틸스터드</v>
@@ -5204,8 +5165,8 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>알루미늄쉬트</v>
@@ -5242,8 +5203,8 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>아크릴패널</v>
@@ -5280,8 +5241,8 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>폴리카보네이트</v>
@@ -5321,8 +5282,8 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B9">
+        <v>2</v>
       </c>
       <c r="C9" t="str">
         <v>에폭시바닥</v>
@@ -5359,8 +5320,8 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B10">
+        <v>2</v>
       </c>
       <c r="C10" t="str">
         <v>유리블록</v>
@@ -5397,8 +5358,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="C11" t="str">
         <v>우레탄바닥</v>
@@ -5435,8 +5396,8 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B12">
+        <v>2</v>
       </c>
       <c r="C12" t="str">
         <v>천연벽지</v>
@@ -5473,8 +5434,8 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>고무타일</v>
@@ -5511,8 +5472,8 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="str">
         <v>재활용알루미늄쉬트</v>
@@ -5549,8 +5510,8 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B15">
+        <v>2</v>
       </c>
       <c r="C15" t="str">
         <v>PVC타일</v>
@@ -5587,8 +5548,8 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
         <v>아연</v>
@@ -5625,8 +5586,8 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="str">
         <v>아크릴시트</v>
@@ -5663,8 +5624,8 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B18">
+        <v>2</v>
       </c>
       <c r="C18" t="str">
         <v>고무바닥재</v>
@@ -5701,8 +5662,8 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>화강석</v>
@@ -5739,8 +5700,8 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B20">
+        <v>2</v>
       </c>
       <c r="C20" t="str">
         <v>인조석</v>
@@ -5777,8 +5738,8 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="str">
         <v>비닐바닥재</v>
@@ -5815,8 +5776,8 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B22">
+        <v>2</v>
       </c>
       <c r="C22" t="str">
         <v>페인트</v>
@@ -5853,8 +5814,8 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B23">
+        <v>2</v>
       </c>
       <c r="C23" t="str">
         <v>벽지</v>
@@ -5888,8 +5849,8 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>Level 2 (≥1000)</v>
+      <c r="B24">
+        <v>2</v>
       </c>
       <c r="C24" t="str">
         <v>GRC패널</v>
@@ -5926,8 +5887,8 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B25">
+        <v>3</v>
       </c>
       <c r="C25" t="str">
         <v>HPL패널</v>
@@ -5964,8 +5925,8 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B26">
+        <v>3</v>
       </c>
       <c r="C26" t="str">
         <v>도기질타일</v>
@@ -6002,8 +5963,8 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B27">
+        <v>3</v>
       </c>
       <c r="C27" t="str">
         <v>세라믹타일</v>
@@ -6040,8 +6001,8 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B28">
+        <v>3</v>
       </c>
       <c r="C28" t="str">
         <v>포세린타일</v>
@@ -6078,8 +6039,8 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B29">
+        <v>3</v>
       </c>
       <c r="C29" t="str">
         <v>테라조</v>
@@ -6116,8 +6077,8 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B30">
+        <v>3</v>
       </c>
       <c r="C30" t="str">
         <v>콘크리트</v>
@@ -6154,8 +6115,8 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B31">
+        <v>3</v>
       </c>
       <c r="C31" t="str">
         <v>시멘트판넬</v>
@@ -6192,8 +6153,8 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B32">
+        <v>3</v>
       </c>
       <c r="C32" t="str">
         <v>흙벽돌</v>
@@ -6230,8 +6191,8 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B33">
+        <v>3</v>
       </c>
       <c r="C33" t="str">
         <v>섬유시멘트사이딩</v>
@@ -6268,8 +6229,8 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B34">
+        <v>3</v>
       </c>
       <c r="C34" t="str">
         <v>점토벽돌</v>
@@ -6306,8 +6267,8 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B35">
+        <v>3</v>
       </c>
       <c r="C35" t="str">
         <v>OSB</v>
@@ -6344,8 +6305,8 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B36">
+        <v>3</v>
       </c>
       <c r="C36" t="str">
         <v>파티클보드</v>
@@ -6382,8 +6343,8 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B37">
+        <v>3</v>
       </c>
       <c r="C37" t="str">
         <v>코르크단열재</v>
@@ -6420,8 +6381,8 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B38">
+        <v>3</v>
       </c>
       <c r="C38" t="str">
         <v>대리석</v>
@@ -6458,8 +6419,8 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B39">
+        <v>3</v>
       </c>
       <c r="C39" t="str">
         <v>규산칼슘보드</v>
@@ -6496,8 +6457,8 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B40">
+        <v>3</v>
       </c>
       <c r="C40" t="str">
         <v>흡음패널</v>
@@ -6534,8 +6495,8 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B41">
+        <v>3</v>
       </c>
       <c r="C41" t="str">
         <v>시멘트미장</v>
@@ -6572,8 +6533,8 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B42">
+        <v>3</v>
       </c>
       <c r="C42" t="str">
         <v>목재스터드</v>
@@ -6610,8 +6571,8 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B43">
+        <v>3</v>
       </c>
       <c r="C43" t="str">
         <v>콘크리트블럭</v>
@@ -6648,8 +6609,8 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B44">
+        <v>3</v>
       </c>
       <c r="C44" t="str">
         <v>경량콘크리트블록</v>
@@ -6686,8 +6647,8 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B45">
+        <v>3</v>
       </c>
       <c r="C45" t="str">
         <v>유리모자이크타일</v>
@@ -6724,8 +6685,8 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B46">
+        <v>3</v>
       </c>
       <c r="C46" t="str">
         <v>점토미장</v>
@@ -6762,8 +6723,8 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B47">
+        <v>3</v>
       </c>
       <c r="C47" t="str">
         <v>ALC블록</v>
@@ -6800,8 +6761,8 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B48">
+        <v>3</v>
       </c>
       <c r="C48" t="str">
         <v>석고미장</v>
@@ -6838,8 +6799,8 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>Level 3 (≥100)</v>
+      <c r="B49">
+        <v>3</v>
       </c>
       <c r="C49" t="str">
         <v>석고보드</v>
@@ -6876,8 +6837,8 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B50">
+        <v>4</v>
       </c>
       <c r="C50" t="str">
         <v>팽창퍼라이트</v>
@@ -6914,8 +6875,8 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B51">
+        <v>4</v>
       </c>
       <c r="C51" t="str">
         <v>라임스톤</v>
@@ -6952,8 +6913,8 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B52">
+        <v>4</v>
       </c>
       <c r="C52" t="str">
         <v>재활용벽돌</v>
@@ -6990,8 +6951,8 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B53">
+        <v>4</v>
       </c>
       <c r="C53" t="str">
         <v>폴리우레탄흡음재</v>
@@ -7028,8 +6989,8 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B54">
+        <v>4</v>
       </c>
       <c r="C54" t="str">
         <v>콘크리트벽돌</v>
@@ -7066,8 +7027,8 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B55">
+        <v>4</v>
       </c>
       <c r="C55" t="str">
         <v>팽창질석</v>
@@ -7104,8 +7065,8 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B56">
+        <v>4</v>
       </c>
       <c r="C56" t="str">
         <v>헴프단열재</v>
@@ -7142,8 +7103,8 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B57">
+        <v>4</v>
       </c>
       <c r="C57" t="str">
         <v>목섬유단열재</v>
@@ -7180,8 +7141,8 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B58">
+        <v>4</v>
       </c>
       <c r="C58" t="str">
         <v>그라스울</v>
@@ -7218,8 +7179,8 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B59">
+        <v>4</v>
       </c>
       <c r="C59" t="str">
         <v>재활용콘크리트</v>
@@ -7256,8 +7217,8 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B60">
+        <v>4</v>
       </c>
       <c r="C60" t="str">
         <v>재사용벽돌</v>
@@ -7294,105 +7255,432 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61" t="str">
+        <v>석회칠</v>
+      </c>
+      <c r="D61" t="str">
+        <v>limewash</v>
+      </c>
+      <c r="E61" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F61" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G61">
+        <v>-10</v>
+      </c>
+      <c r="H61" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I61">
+        <v>1400</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="L61" t="str">
+        <v>ICE v3</v>
+      </c>
+      <c r="N61" t="str">
+        <v>탄산화 -10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B62">
+        <v>5</v>
+      </c>
+      <c r="C62" t="str">
+        <v>석회미장</v>
+      </c>
+      <c r="D62" t="str">
+        <v>lime_plaster</v>
+      </c>
+      <c r="E62" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F62" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G62">
+        <v>-25</v>
+      </c>
+      <c r="H62" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I62">
+        <v>1600</v>
+      </c>
+      <c r="J62">
+        <v>15</v>
+      </c>
+      <c r="L62" t="str">
+        <v>ICE v3</v>
+      </c>
+      <c r="N62" t="str">
+        <v>석회 탄산화 -25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B63">
+        <v>5</v>
+      </c>
+      <c r="C63" t="str">
+        <v>셀룰로오스단열</v>
+      </c>
+      <c r="D63" t="str">
+        <v>cellulose_insulation</v>
+      </c>
+      <c r="E63" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F63" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G63">
+        <v>-26</v>
+      </c>
+      <c r="H63" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I63">
+        <v>50</v>
+      </c>
+      <c r="J63">
+        <v>100</v>
+      </c>
+      <c r="L63" t="str">
+        <v>EC3 추정</v>
+      </c>
+      <c r="N63" t="str">
+        <v>바이오제닉 -0.52 × 50 = -26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B64">
+        <v>5</v>
+      </c>
+      <c r="C64" t="str">
+        <v>양모단열재</v>
+      </c>
+      <c r="D64" t="str">
+        <v>wool_insulation</v>
+      </c>
+      <c r="E64" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F64" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G64">
+        <v>-54</v>
+      </c>
+      <c r="H64" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I64">
+        <v>25</v>
+      </c>
+      <c r="J64">
+        <v>100</v>
+      </c>
+      <c r="L64" t="str">
+        <v>ICE v3</v>
+      </c>
+      <c r="N64" t="str">
+        <v>-2.16 × 25 = -54</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B65">
+        <v>5</v>
+      </c>
+      <c r="C65" t="str">
+        <v>볏짚단열</v>
+      </c>
+      <c r="D65" t="str">
+        <v>straw_insulation</v>
+      </c>
+      <c r="E65" t="str">
+        <v>insulation</v>
+      </c>
+      <c r="F65" t="str">
+        <v>단열재</v>
+      </c>
+      <c r="G65">
+        <v>-100</v>
+      </c>
+      <c r="H65" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I65">
+        <v>80</v>
+      </c>
+      <c r="J65">
+        <v>100</v>
+      </c>
+      <c r="L65" t="str">
+        <v>학술논문</v>
+      </c>
+      <c r="N65" t="str">
+        <v>바이오제닉 -100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="str">
+        <v>헴프크리트</v>
+      </c>
+      <c r="D66" t="str">
+        <v>hempcrete</v>
+      </c>
+      <c r="E66" t="str">
+        <v>structural</v>
+      </c>
+      <c r="F66" t="str">
+        <v>구조재</v>
+      </c>
+      <c r="G66">
+        <v>-110</v>
+      </c>
+      <c r="H66" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I66">
+        <v>500</v>
+      </c>
+      <c r="J66">
+        <v>200</v>
+      </c>
+      <c r="L66" t="str">
+        <v>학술논문 추정</v>
+      </c>
+      <c r="N66" t="str">
+        <v>헴프크리트: 바이오제닉 포함 약 -110 kgCO2e/m³. m²(200mm): -110×0.2=-22 kgCO2e/m²</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="str">
-        <v>Level 4 (≥0)</v>
-      </c>
-      <c r="K67" t="str">
-        <v>○</v>
+      <c r="B67">
+        <v>5</v>
+      </c>
+      <c r="C67" t="str">
+        <v>천연고무바닥</v>
+      </c>
+      <c r="D67" t="str">
+        <v>natural_rubber_flooring</v>
+      </c>
+      <c r="E67" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F67" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G67">
+        <v>-120</v>
+      </c>
+      <c r="H67" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I67">
+        <v>930</v>
+      </c>
+      <c r="J67">
+        <v>3</v>
+      </c>
+      <c r="L67" t="str">
+        <v>EC3 (Recycled Rubber 역산)</v>
+      </c>
+      <c r="N67" t="str">
+        <v>천연고무 바이오제닉 포함 -120 kgCO2e/m³</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B68">
+        <v>5</v>
+      </c>
+      <c r="C68" t="str">
+        <v>코르크바닥</v>
+      </c>
+      <c r="D68" t="str">
+        <v>cork_flooring</v>
+      </c>
+      <c r="E68" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F68" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G68">
+        <v>-195</v>
+      </c>
+      <c r="H68" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I68">
+        <v>500</v>
+      </c>
+      <c r="J68">
+        <v>6</v>
+      </c>
+      <c r="L68" t="str">
+        <v>ICE v3</v>
+      </c>
+      <c r="N68" t="str">
+        <v>바이오제닉 -0.39 × 500 = -195</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B69">
+        <v>5</v>
+      </c>
+      <c r="C69" t="str">
+        <v>MDF</v>
+      </c>
+      <c r="D69" t="str">
+        <v>mdf</v>
+      </c>
+      <c r="E69" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F69" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G69">
+        <v>-226.67</v>
+      </c>
+      <c r="H69" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I69">
+        <v>700</v>
+      </c>
+      <c r="J69">
+        <v>15</v>
+      </c>
+      <c r="L69" t="str">
+        <v>2050materials (ceiling 우선)</v>
+      </c>
+      <c r="N69" t="str">
+        <v>-3.4 kgCO2e/m² ÷ 0.015m(15mm) = -226.7 kgCO2e/m³ (2050materials, ceiling 탭 우선적용)</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B70">
+        <v>5</v>
+      </c>
+      <c r="C70" t="str">
+        <v>에코보드</v>
+      </c>
+      <c r="D70" t="str">
+        <v>eco_board</v>
+      </c>
+      <c r="E70" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F70" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G70">
+        <v>-300</v>
+      </c>
+      <c r="H70" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I70">
+        <v>600</v>
+      </c>
+      <c r="J70">
+        <v>18</v>
+      </c>
+      <c r="L70" t="str">
+        <v>EC3 추정</v>
+      </c>
+      <c r="N70" t="str">
+        <v>재활용목재 -300</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="str">
-        <v>Level 4 (≥0)</v>
+      <c r="B71">
+        <v>5</v>
+      </c>
+      <c r="C71" t="str">
+        <v>대나무마루</v>
+      </c>
+      <c r="D71" t="str">
+        <v>bamboo_flooring</v>
+      </c>
+      <c r="E71" t="str">
+        <v>finishing</v>
+      </c>
+      <c r="F71" t="str">
+        <v>마감재</v>
+      </c>
+      <c r="G71">
+        <v>-350</v>
+      </c>
+      <c r="H71" t="str">
+        <v>kgCO2e/m³</v>
+      </c>
+      <c r="I71">
+        <v>700</v>
+      </c>
+      <c r="J71">
+        <v>15</v>
+      </c>
+      <c r="L71" t="str">
+        <v>EC3 추정</v>
+      </c>
+      <c r="N71" t="str">
+        <v>바이오제닉 -0.5 × 700 = -350</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B72">
+        <v>5</v>
       </c>
       <c r="C72" t="str">
-        <v>석회칠</v>
+        <v>대나무패널</v>
       </c>
       <c r="D72" t="str">
-        <v>limewash</v>
+        <v>bamboo_panel</v>
       </c>
       <c r="E72" t="str">
         <v>finishing</v>
@@ -7401,36 +7689,36 @@
         <v>마감재</v>
       </c>
       <c r="G72">
-        <v>-10</v>
+        <v>-350</v>
       </c>
       <c r="H72" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I72">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="J72">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L72" t="str">
-        <v>ICE v3</v>
+        <v>EC3 추정</v>
       </c>
       <c r="N72" t="str">
-        <v>탄산화 -10</v>
+        <v>바이오제닉 -0.5 × 700 = -350</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B73">
+        <v>5</v>
       </c>
       <c r="C73" t="str">
-        <v>석회미장</v>
+        <v>대나무보드</v>
       </c>
       <c r="D73" t="str">
-        <v>lime_plaster</v>
+        <v>bamboo_board</v>
       </c>
       <c r="E73" t="str">
         <v>finishing</v>
@@ -7439,188 +7727,188 @@
         <v>마감재</v>
       </c>
       <c r="G73">
-        <v>-25</v>
+        <v>-350</v>
       </c>
       <c r="H73" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I73">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="J73">
         <v>15</v>
       </c>
       <c r="L73" t="str">
-        <v>ICE v3</v>
+        <v>EC3 (dasso Traditional Bamboo)</v>
       </c>
       <c r="N73" t="str">
-        <v>석회 탄산화 -25</v>
+        <v>0.852 kgCO2e/0.0735m³ → 11.6 kgCO2e/m³ fossil, 바이오제닉 포함 -350</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B74">
+        <v>5</v>
       </c>
       <c r="C74" t="str">
-        <v>셀룰로오스단열</v>
+        <v>리놀륨</v>
       </c>
       <c r="D74" t="str">
-        <v>cellulose_insulation</v>
+        <v>linoleum</v>
       </c>
       <c r="E74" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F74" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G74">
-        <v>-26</v>
+        <v>-360</v>
       </c>
       <c r="H74" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I74">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="J74">
-        <v>100</v>
+        <v>2.5</v>
       </c>
       <c r="L74" t="str">
-        <v>EC3 추정</v>
+        <v>ICE v3</v>
       </c>
       <c r="N74" t="str">
-        <v>바이오제닉 -0.52 × 50 = -26</v>
+        <v>바이오제닉 -0.3 × 1200 = -360</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B75">
+        <v>5</v>
       </c>
       <c r="C75" t="str">
-        <v>양모단열재</v>
+        <v>목모보드</v>
       </c>
       <c r="D75" t="str">
-        <v>wool_insulation</v>
+        <v>wood_wool_board</v>
       </c>
       <c r="E75" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F75" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G75">
-        <v>-54</v>
+        <v>-368</v>
       </c>
       <c r="H75" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I75">
+        <v>350</v>
+      </c>
+      <c r="J75">
         <v>25</v>
       </c>
-      <c r="J75">
-        <v>100</v>
-      </c>
       <c r="L75" t="str">
-        <v>ICE v3</v>
+        <v>EC3 (ceiling 우선)</v>
       </c>
       <c r="N75" t="str">
-        <v>-2.16 × 25 = -54</v>
+        <v>-9.2 kgCO2e/m² ÷ 0.025m(25mm) = -368.0 kgCO2e/m³ (EC3, ceiling 탭 우선적용)</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B76">
+        <v>5</v>
       </c>
       <c r="C76" t="str">
-        <v>볏짚단열</v>
+        <v>원목마루</v>
       </c>
       <c r="D76" t="str">
-        <v>straw_insulation</v>
+        <v>solid_wood_flooring</v>
       </c>
       <c r="E76" t="str">
-        <v>insulation</v>
+        <v>finishing</v>
       </c>
       <c r="F76" t="str">
-        <v>단열재</v>
+        <v>마감재</v>
       </c>
       <c r="G76">
-        <v>-100</v>
+        <v>-480</v>
       </c>
       <c r="H76" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I76">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="J76">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="L76" t="str">
-        <v>학술논문</v>
+        <v>EC3</v>
       </c>
       <c r="N76" t="str">
-        <v>바이오제닉 -100</v>
+        <v>바이오제닉 -0.8 × 600 = -480</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B77">
+        <v>5</v>
       </c>
       <c r="C77" t="str">
-        <v>헴프크리트</v>
+        <v>천연리놀륨</v>
       </c>
       <c r="D77" t="str">
-        <v>hempcrete</v>
+        <v>natural_linoleum</v>
       </c>
       <c r="E77" t="str">
-        <v>structural</v>
+        <v>finishing</v>
       </c>
       <c r="F77" t="str">
-        <v>구조재</v>
+        <v>마감재</v>
       </c>
       <c r="G77">
-        <v>-110</v>
+        <v>-500</v>
       </c>
       <c r="H77" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I77">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="J77">
-        <v>200</v>
+        <v>2.5</v>
       </c>
       <c r="L77" t="str">
-        <v>학술논문 추정</v>
+        <v>ICE v3</v>
       </c>
       <c r="N77" t="str">
-        <v>헴프크리트: 바이오제닉 포함 약 -110 kgCO2e/m³. m²(200mm): -110×0.2=-22 kgCO2e/m²</v>
+        <v>아마인유 기반 -500</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B78">
+        <v>5</v>
       </c>
       <c r="C78" t="str">
-        <v>천연고무바닥</v>
+        <v>삼나무판</v>
       </c>
       <c r="D78" t="str">
-        <v>natural_rubber_flooring</v>
+        <v>cedar_board</v>
       </c>
       <c r="E78" t="str">
         <v>finishing</v>
@@ -7629,36 +7917,36 @@
         <v>마감재</v>
       </c>
       <c r="G78">
-        <v>-120</v>
+        <v>-520</v>
       </c>
       <c r="H78" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I78">
-        <v>930</v>
+        <v>350</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L78" t="str">
-        <v>EC3 (Recycled Rubber 역산)</v>
+        <v>EC3 추정</v>
       </c>
       <c r="N78" t="str">
-        <v>천연고무 바이오제닉 포함 -120 kgCO2e/m³</v>
+        <v>바이오제닉 -1.49 × 350 = -520</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B79">
+        <v>5</v>
       </c>
       <c r="C79" t="str">
-        <v>코르크바닥</v>
+        <v>적삼목판</v>
       </c>
       <c r="D79" t="str">
-        <v>cork_flooring</v>
+        <v>western_red_cedar_board</v>
       </c>
       <c r="E79" t="str">
         <v>finishing</v>
@@ -7667,150 +7955,150 @@
         <v>마감재</v>
       </c>
       <c r="G79">
-        <v>-195</v>
+        <v>-550</v>
       </c>
       <c r="H79" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I79">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="J79">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L79" t="str">
-        <v>ICE v3</v>
+        <v>EC3 추정</v>
       </c>
       <c r="N79" t="str">
-        <v>바이오제닉 -0.39 × 500 = -195</v>
+        <v>바이오제닉 -1.45 × 380 = -550</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B80">
+        <v>5</v>
       </c>
       <c r="C80" t="str">
-        <v>MDF</v>
+        <v>집성목</v>
       </c>
       <c r="D80" t="str">
-        <v>mdf</v>
+        <v>glulam</v>
       </c>
       <c r="E80" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F80" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G80">
-        <v>-226.67</v>
+        <v>-650</v>
       </c>
       <c r="H80" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I80">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J80">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="L80" t="str">
-        <v>2050materials (ceiling 우선)</v>
+        <v>EC3</v>
       </c>
       <c r="N80" t="str">
-        <v>-3.4 kgCO2e/m² ÷ 0.015m(15mm) = -226.7 kgCO2e/m³ (2050materials, ceiling 탭 우선적용)</v>
+        <v>집성목 -650 (바이오제닉)</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B81">
+        <v>5</v>
       </c>
       <c r="C81" t="str">
-        <v>에코보드</v>
+        <v>LVL</v>
       </c>
       <c r="D81" t="str">
-        <v>eco_board</v>
+        <v>lvl</v>
       </c>
       <c r="E81" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F81" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G81">
-        <v>-300</v>
+        <v>-680</v>
       </c>
       <c r="H81" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I81">
-        <v>600</v>
+        <v>510</v>
       </c>
       <c r="J81">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="L81" t="str">
-        <v>EC3 추정</v>
+        <v>EC3</v>
       </c>
       <c r="N81" t="str">
-        <v>재활용목재 -300</v>
+        <v>LVL -680 (바이오제닉)</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B82">
+        <v>5</v>
       </c>
       <c r="C82" t="str">
-        <v>대나무마루</v>
+        <v>CLT</v>
       </c>
       <c r="D82" t="str">
-        <v>bamboo_flooring</v>
+        <v>clt</v>
       </c>
       <c r="E82" t="str">
-        <v>finishing</v>
+        <v>structural</v>
       </c>
       <c r="F82" t="str">
-        <v>마감재</v>
+        <v>구조재</v>
       </c>
       <c r="G82">
-        <v>-350</v>
+        <v>-700</v>
       </c>
       <c r="H82" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I82">
-        <v>700</v>
+        <v>470</v>
       </c>
       <c r="J82">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="L82" t="str">
-        <v>EC3 추정</v>
+        <v>EC3</v>
       </c>
       <c r="N82" t="str">
-        <v>바이오제닉 -0.5 × 700 = -350</v>
+        <v>CLT -700 (바이오제닉)</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B83">
+        <v>5</v>
       </c>
       <c r="C83" t="str">
-        <v>대나무패널</v>
+        <v>합판</v>
       </c>
       <c r="D83" t="str">
-        <v>bamboo_panel</v>
+        <v>plywood</v>
       </c>
       <c r="E83" t="str">
         <v>finishing</v>
@@ -7819,564 +8107,65 @@
         <v>마감재</v>
       </c>
       <c r="G83">
-        <v>-350</v>
+        <v>-733.33</v>
       </c>
       <c r="H83" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I83">
-        <v>700</v>
+        <v>620</v>
       </c>
       <c r="J83">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L83" t="str">
-        <v>EC3 추정</v>
+        <v>EC3 (ceiling 우선)</v>
       </c>
       <c r="N83" t="str">
-        <v>바이오제닉 -0.5 × 700 = -350</v>
+        <v>-8.8 kgCO2e/m² ÷ 0.012m(12mm) = -733.3 kgCO2e/m³ (EC3, ceiling 탭 우선적용)</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="str">
-        <v>Level 5 (&lt;0)</v>
+      <c r="B84">
+        <v>5</v>
       </c>
       <c r="C84" t="str">
-        <v>대나무보드</v>
+        <v>볏짚단열패널</v>
       </c>
       <c r="D84" t="str">
-        <v>bamboo_board</v>
+        <v>straw_insulation_panel</v>
       </c>
       <c r="E84" t="str">
-        <v>finishing</v>
+        <v>insulation</v>
       </c>
       <c r="F84" t="str">
-        <v>마감재</v>
+        <v>단열재</v>
       </c>
       <c r="G84">
-        <v>-350</v>
+        <v>-887</v>
       </c>
       <c r="H84" t="str">
         <v>kgCO2e/m³</v>
       </c>
       <c r="I84">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="J84">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="L84" t="str">
-        <v>EC3 (dasso Traditional Bamboo)</v>
+        <v>EC3 (EcoCocon Straw Modules)</v>
       </c>
       <c r="N84" t="str">
-        <v>0.852 kgCO2e/0.0735m³ → 11.6 kgCO2e/m³ fossil, 바이오제닉 포함 -350</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C85" t="str">
-        <v>리놀륨</v>
-      </c>
-      <c r="D85" t="str">
-        <v>linoleum</v>
-      </c>
-      <c r="E85" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F85" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G85">
-        <v>-360</v>
-      </c>
-      <c r="H85" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I85">
-        <v>1200</v>
-      </c>
-      <c r="J85">
-        <v>2.5</v>
-      </c>
-      <c r="L85" t="str">
-        <v>ICE v3</v>
-      </c>
-      <c r="N85" t="str">
-        <v>바이오제닉 -0.3 × 1200 = -360</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C86" t="str">
-        <v>목모보드</v>
-      </c>
-      <c r="D86" t="str">
-        <v>wood_wool_board</v>
-      </c>
-      <c r="E86" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F86" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G86">
-        <v>-368</v>
-      </c>
-      <c r="H86" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I86">
-        <v>350</v>
-      </c>
-      <c r="J86">
-        <v>25</v>
-      </c>
-      <c r="L86" t="str">
-        <v>EC3 (ceiling 우선)</v>
-      </c>
-      <c r="N86" t="str">
-        <v>-9.2 kgCO2e/m² ÷ 0.025m(25mm) = -368.0 kgCO2e/m³ (EC3, ceiling 탭 우선적용)</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C87" t="str">
-        <v>원목마루</v>
-      </c>
-      <c r="D87" t="str">
-        <v>solid_wood_flooring</v>
-      </c>
-      <c r="E87" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F87" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G87">
-        <v>-480</v>
-      </c>
-      <c r="H87" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I87">
-        <v>600</v>
-      </c>
-      <c r="J87">
-        <v>15</v>
-      </c>
-      <c r="L87" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N87" t="str">
-        <v>바이오제닉 -0.8 × 600 = -480</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C88" t="str">
-        <v>천연리놀륨</v>
-      </c>
-      <c r="D88" t="str">
-        <v>natural_linoleum</v>
-      </c>
-      <c r="E88" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F88" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G88">
-        <v>-500</v>
-      </c>
-      <c r="H88" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I88">
-        <v>1200</v>
-      </c>
-      <c r="J88">
-        <v>2.5</v>
-      </c>
-      <c r="L88" t="str">
-        <v>ICE v3</v>
-      </c>
-      <c r="N88" t="str">
-        <v>아마인유 기반 -500</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C89" t="str">
-        <v>삼나무판</v>
-      </c>
-      <c r="D89" t="str">
-        <v>cedar_board</v>
-      </c>
-      <c r="E89" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F89" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G89">
-        <v>-520</v>
-      </c>
-      <c r="H89" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I89">
-        <v>350</v>
-      </c>
-      <c r="J89">
-        <v>18</v>
-      </c>
-      <c r="L89" t="str">
-        <v>EC3 추정</v>
-      </c>
-      <c r="N89" t="str">
-        <v>바이오제닉 -1.49 × 350 = -520</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C90" t="str">
-        <v>적삼목판</v>
-      </c>
-      <c r="D90" t="str">
-        <v>western_red_cedar_board</v>
-      </c>
-      <c r="E90" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F90" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G90">
-        <v>-550</v>
-      </c>
-      <c r="H90" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I90">
-        <v>380</v>
-      </c>
-      <c r="J90">
-        <v>18</v>
-      </c>
-      <c r="L90" t="str">
-        <v>EC3 추정</v>
-      </c>
-      <c r="N90" t="str">
-        <v>바이오제닉 -1.45 × 380 = -550</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C91" t="str">
-        <v>집성목</v>
-      </c>
-      <c r="D91" t="str">
-        <v>glulam</v>
-      </c>
-      <c r="E91" t="str">
-        <v>structural</v>
-      </c>
-      <c r="F91" t="str">
-        <v>구조재</v>
-      </c>
-      <c r="G91">
-        <v>-650</v>
-      </c>
-      <c r="H91" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I91">
-        <v>500</v>
-      </c>
-      <c r="J91">
-        <v>40</v>
-      </c>
-      <c r="L91" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N91" t="str">
-        <v>집성목 -650 (바이오제닉)</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C92" t="str">
-        <v>LVL</v>
-      </c>
-      <c r="D92" t="str">
-        <v>lvl</v>
-      </c>
-      <c r="E92" t="str">
-        <v>structural</v>
-      </c>
-      <c r="F92" t="str">
-        <v>구조재</v>
-      </c>
-      <c r="G92">
-        <v>-680</v>
-      </c>
-      <c r="H92" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I92">
-        <v>510</v>
-      </c>
-      <c r="J92">
-        <v>45</v>
-      </c>
-      <c r="L92" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N92" t="str">
-        <v>LVL -680 (바이오제닉)</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C93" t="str">
-        <v>CLT</v>
-      </c>
-      <c r="D93" t="str">
-        <v>clt</v>
-      </c>
-      <c r="E93" t="str">
-        <v>structural</v>
-      </c>
-      <c r="F93" t="str">
-        <v>구조재</v>
-      </c>
-      <c r="G93">
-        <v>-700</v>
-      </c>
-      <c r="H93" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I93">
-        <v>470</v>
-      </c>
-      <c r="J93">
-        <v>100</v>
-      </c>
-      <c r="L93" t="str">
-        <v>EC3</v>
-      </c>
-      <c r="N93" t="str">
-        <v>CLT -700 (바이오제닉)</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C94" t="str">
-        <v>합판</v>
-      </c>
-      <c r="D94" t="str">
-        <v>plywood</v>
-      </c>
-      <c r="E94" t="str">
-        <v>finishing</v>
-      </c>
-      <c r="F94" t="str">
-        <v>마감재</v>
-      </c>
-      <c r="G94">
-        <v>-733.33</v>
-      </c>
-      <c r="H94" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I94">
-        <v>620</v>
-      </c>
-      <c r="J94">
-        <v>12</v>
-      </c>
-      <c r="L94" t="str">
-        <v>EC3 (ceiling 우선)</v>
-      </c>
-      <c r="N94" t="str">
-        <v>-8.8 kgCO2e/m² ÷ 0.012m(12mm) = -733.3 kgCO2e/m³ (EC3, ceiling 탭 우선적용)</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-      <c r="C95" t="str">
-        <v>볏짚단열패널</v>
-      </c>
-      <c r="D95" t="str">
-        <v>straw_insulation_panel</v>
-      </c>
-      <c r="E95" t="str">
-        <v>insulation</v>
-      </c>
-      <c r="F95" t="str">
-        <v>단열재</v>
-      </c>
-      <c r="G95">
-        <v>-887</v>
-      </c>
-      <c r="H95" t="str">
-        <v>kgCO2e/m³</v>
-      </c>
-      <c r="I95">
-        <v>150</v>
-      </c>
-      <c r="J95">
-        <v>100</v>
-      </c>
-      <c r="L95" t="str">
-        <v>EC3 (EcoCocon Straw Modules)</v>
-      </c>
-      <c r="N95" t="str">
         <v>-88.7 kgCO2e/m² ÷ 0.1 = -887 kgCO2e/m³</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104">
-        <v>103</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Level 5 (&lt;0)</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N84"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9134,2052 +8923,323 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C30" t="str">
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v/>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <v/>
-      </c>
-      <c r="G33" t="str">
-        <v/>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <v/>
-      </c>
-      <c r="K33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-      <c r="F34" t="str">
-        <v/>
-      </c>
-      <c r="G34" t="str">
-        <v/>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
-      <c r="K34" t="str">
-        <v/>
-      </c>
-      <c r="L34" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C36" t="str">
-        <v/>
-      </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
-      <c r="F36" t="str">
-        <v/>
-      </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <v/>
-      </c>
-      <c r="K36" t="str">
-        <v/>
-      </c>
-      <c r="L36" t="str">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C37" t="str">
-        <v/>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
-      <c r="I37" t="str">
-        <v/>
-      </c>
-      <c r="K37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C38" t="str">
-        <v/>
-      </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-      <c r="F38" t="str">
-        <v/>
-      </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38" t="str">
-        <v/>
-      </c>
-      <c r="K38" t="str">
-        <v/>
-      </c>
-      <c r="L38" t="str">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v/>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40" t="str">
-        <v/>
-      </c>
-      <c r="K40" t="str">
-        <v/>
-      </c>
-      <c r="L40" t="str">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
-      <c r="C42" t="str">
-        <v/>
-      </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="K43" t="str">
-        <v/>
-      </c>
-      <c r="L43" t="str">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v/>
-      </c>
-      <c r="K44" t="str">
-        <v/>
-      </c>
-      <c r="L44" t="str">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C45" t="str">
-        <v/>
-      </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
-      <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
-        <v/>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C46" t="str">
-        <v/>
-      </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v/>
-      </c>
-      <c r="G46" t="str">
-        <v/>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-      <c r="I46" t="str">
-        <v/>
-      </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-      <c r="L46" t="str">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C47" t="str">
-        <v/>
-      </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47" t="str">
-        <v/>
-      </c>
-      <c r="H47" t="str">
-        <v/>
-      </c>
-      <c r="I47" t="str">
-        <v/>
-      </c>
-      <c r="K47" t="str">
-        <v/>
-      </c>
-      <c r="L47" t="str">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C48" t="str">
-        <v/>
-      </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48" t="str">
-        <v/>
-      </c>
-      <c r="H48" t="str">
-        <v/>
-      </c>
-      <c r="I48" t="str">
-        <v/>
-      </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
-      <c r="L48" t="str">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="E49" t="str">
-        <v/>
-      </c>
-      <c r="F49" t="str">
-        <v/>
-      </c>
-      <c r="G49" t="str">
-        <v/>
-      </c>
-      <c r="H49" t="str">
-        <v/>
-      </c>
-      <c r="I49" t="str">
-        <v/>
-      </c>
-      <c r="K49" t="str">
-        <v/>
-      </c>
-      <c r="L49" t="str">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="E50" t="str">
-        <v/>
-      </c>
-      <c r="F50" t="str">
-        <v/>
-      </c>
-      <c r="G50" t="str">
-        <v/>
-      </c>
-      <c r="H50" t="str">
-        <v/>
-      </c>
-      <c r="I50" t="str">
-        <v/>
-      </c>
-      <c r="K50" t="str">
-        <v/>
-      </c>
-      <c r="L50" t="str">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C51" t="str">
-        <v/>
-      </c>
-      <c r="E51" t="str">
-        <v/>
-      </c>
-      <c r="F51" t="str">
-        <v/>
-      </c>
-      <c r="G51" t="str">
-        <v/>
-      </c>
-      <c r="H51" t="str">
-        <v/>
-      </c>
-      <c r="I51" t="str">
-        <v/>
-      </c>
-      <c r="K51" t="str">
-        <v/>
-      </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
-      <c r="I52" t="str">
-        <v/>
-      </c>
-      <c r="K52" t="str">
-        <v/>
-      </c>
-      <c r="L52" t="str">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
-        <v/>
-      </c>
-      <c r="H53" t="str">
-        <v/>
-      </c>
-      <c r="I53" t="str">
-        <v/>
-      </c>
-      <c r="K53" t="str">
-        <v/>
-      </c>
-      <c r="L53" t="str">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
-      </c>
-      <c r="G54" t="str">
-        <v/>
-      </c>
-      <c r="H54" t="str">
-        <v/>
-      </c>
-      <c r="I54" t="str">
-        <v/>
-      </c>
-      <c r="K54" t="str">
-        <v/>
-      </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="E55" t="str">
-        <v/>
-      </c>
-      <c r="F55" t="str">
-        <v/>
-      </c>
-      <c r="G55" t="str">
-        <v/>
-      </c>
-      <c r="H55" t="str">
-        <v/>
-      </c>
-      <c r="I55" t="str">
-        <v/>
-      </c>
-      <c r="K55" t="str">
-        <v/>
-      </c>
-      <c r="L55" t="str">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="E56" t="str">
-        <v/>
-      </c>
-      <c r="F56" t="str">
-        <v/>
-      </c>
-      <c r="G56" t="str">
-        <v/>
-      </c>
-      <c r="H56" t="str">
-        <v/>
-      </c>
-      <c r="I56" t="str">
-        <v/>
-      </c>
-      <c r="K56" t="str">
-        <v/>
-      </c>
-      <c r="L56" t="str">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="E57" t="str">
-        <v/>
-      </c>
-      <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
-      <c r="I57" t="str">
-        <v/>
-      </c>
-      <c r="K57" t="str">
-        <v/>
-      </c>
-      <c r="L57" t="str">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-      <c r="F58" t="str">
-        <v/>
-      </c>
-      <c r="G58" t="str">
-        <v/>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-      <c r="I58" t="str">
-        <v/>
-      </c>
-      <c r="K58" t="str">
-        <v/>
-      </c>
-      <c r="L58" t="str">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-      <c r="K59" t="str">
-        <v/>
-      </c>
-      <c r="L59" t="str">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v/>
-      </c>
-      <c r="G60" t="str">
-        <v/>
-      </c>
-      <c r="H60" t="str">
-        <v/>
-      </c>
-      <c r="I60" t="str">
-        <v/>
-      </c>
-      <c r="K60" t="str">
-        <v/>
-      </c>
-      <c r="L60" t="str">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="E61" t="str">
-        <v/>
-      </c>
-      <c r="F61" t="str">
-        <v/>
-      </c>
-      <c r="G61" t="str">
-        <v/>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
-      <c r="I61" t="str">
-        <v/>
-      </c>
-      <c r="K61" t="str">
-        <v/>
-      </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C62" t="str">
-        <v/>
-      </c>
-      <c r="E62" t="str">
-        <v/>
-      </c>
-      <c r="F62" t="str">
-        <v/>
-      </c>
-      <c r="G62" t="str">
-        <v/>
-      </c>
-      <c r="H62" t="str">
-        <v/>
-      </c>
-      <c r="I62" t="str">
-        <v/>
-      </c>
-      <c r="K62" t="str">
-        <v/>
-      </c>
-      <c r="L62" t="str">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C63" t="str">
-        <v/>
-      </c>
-      <c r="E63" t="str">
-        <v/>
-      </c>
-      <c r="F63" t="str">
-        <v/>
-      </c>
-      <c r="G63" t="str">
-        <v/>
-      </c>
-      <c r="H63" t="str">
-        <v/>
-      </c>
-      <c r="I63" t="str">
-        <v/>
-      </c>
-      <c r="K63" t="str">
-        <v/>
-      </c>
-      <c r="L63" t="str">
-        <v/>
-      </c>
     </row>
     <row r="64">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C64" t="str">
-        <v/>
-      </c>
-      <c r="E64" t="str">
-        <v/>
-      </c>
-      <c r="F64" t="str">
-        <v/>
-      </c>
-      <c r="G64" t="str">
-        <v/>
-      </c>
-      <c r="H64" t="str">
-        <v/>
-      </c>
-      <c r="I64" t="str">
-        <v/>
-      </c>
-      <c r="K64" t="str">
-        <v/>
-      </c>
-      <c r="L64" t="str">
-        <v/>
-      </c>
     </row>
     <row r="65">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C65" t="str">
-        <v/>
-      </c>
-      <c r="E65" t="str">
-        <v/>
-      </c>
-      <c r="F65" t="str">
-        <v/>
-      </c>
-      <c r="G65" t="str">
-        <v/>
-      </c>
-      <c r="H65" t="str">
-        <v/>
-      </c>
-      <c r="I65" t="str">
-        <v/>
-      </c>
-      <c r="K65" t="str">
-        <v/>
-      </c>
-      <c r="L65" t="str">
-        <v/>
-      </c>
     </row>
     <row r="66">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C66" t="str">
-        <v/>
-      </c>
-      <c r="E66" t="str">
-        <v/>
-      </c>
-      <c r="F66" t="str">
-        <v/>
-      </c>
-      <c r="G66" t="str">
-        <v/>
-      </c>
-      <c r="H66" t="str">
-        <v/>
-      </c>
-      <c r="I66" t="str">
-        <v/>
-      </c>
-      <c r="K66" t="str">
-        <v/>
-      </c>
-      <c r="L66" t="str">
-        <v/>
-      </c>
     </row>
     <row r="67">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C67" t="str">
-        <v/>
-      </c>
-      <c r="E67" t="str">
-        <v/>
-      </c>
-      <c r="F67" t="str">
-        <v/>
-      </c>
-      <c r="G67" t="str">
-        <v/>
-      </c>
-      <c r="H67" t="str">
-        <v/>
-      </c>
-      <c r="I67" t="str">
-        <v/>
-      </c>
-      <c r="K67" t="str">
-        <v/>
-      </c>
-      <c r="L67" t="str">
-        <v/>
-      </c>
     </row>
     <row r="68">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="E68" t="str">
-        <v/>
-      </c>
-      <c r="F68" t="str">
-        <v/>
-      </c>
-      <c r="G68" t="str">
-        <v/>
-      </c>
-      <c r="H68" t="str">
-        <v/>
-      </c>
-      <c r="I68" t="str">
-        <v/>
-      </c>
-      <c r="K68" t="str">
-        <v/>
-      </c>
-      <c r="L68" t="str">
-        <v/>
-      </c>
     </row>
     <row r="69">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C69" t="str">
-        <v/>
-      </c>
-      <c r="E69" t="str">
-        <v/>
-      </c>
-      <c r="F69" t="str">
-        <v/>
-      </c>
-      <c r="G69" t="str">
-        <v/>
-      </c>
-      <c r="H69" t="str">
-        <v/>
-      </c>
-      <c r="I69" t="str">
-        <v/>
-      </c>
-      <c r="K69" t="str">
-        <v/>
-      </c>
-      <c r="L69" t="str">
-        <v/>
-      </c>
     </row>
     <row r="70">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="E70" t="str">
-        <v/>
-      </c>
-      <c r="F70" t="str">
-        <v/>
-      </c>
-      <c r="G70" t="str">
-        <v/>
-      </c>
-      <c r="H70" t="str">
-        <v/>
-      </c>
-      <c r="I70" t="str">
-        <v/>
-      </c>
-      <c r="K70" t="str">
-        <v/>
-      </c>
-      <c r="L70" t="str">
-        <v/>
-      </c>
     </row>
     <row r="71">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="E71" t="str">
-        <v/>
-      </c>
-      <c r="F71" t="str">
-        <v/>
-      </c>
-      <c r="G71" t="str">
-        <v/>
-      </c>
-      <c r="H71" t="str">
-        <v/>
-      </c>
-      <c r="I71" t="str">
-        <v/>
-      </c>
-      <c r="K71" t="str">
-        <v/>
-      </c>
-      <c r="L71" t="str">
-        <v/>
-      </c>
     </row>
     <row r="72">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="E72" t="str">
-        <v/>
-      </c>
-      <c r="F72" t="str">
-        <v/>
-      </c>
-      <c r="G72" t="str">
-        <v/>
-      </c>
-      <c r="H72" t="str">
-        <v/>
-      </c>
-      <c r="I72" t="str">
-        <v/>
-      </c>
-      <c r="K72" t="str">
-        <v/>
-      </c>
-      <c r="L72" t="str">
-        <v/>
-      </c>
     </row>
     <row r="73">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C73" t="str">
-        <v/>
-      </c>
-      <c r="E73" t="str">
-        <v/>
-      </c>
-      <c r="F73" t="str">
-        <v/>
-      </c>
-      <c r="G73" t="str">
-        <v/>
-      </c>
-      <c r="H73" t="str">
-        <v/>
-      </c>
-      <c r="I73" t="str">
-        <v/>
-      </c>
-      <c r="K73" t="str">
-        <v/>
-      </c>
-      <c r="L73" t="str">
-        <v/>
-      </c>
     </row>
     <row r="74">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C74" t="str">
-        <v/>
-      </c>
-      <c r="E74" t="str">
-        <v/>
-      </c>
-      <c r="F74" t="str">
-        <v/>
-      </c>
-      <c r="G74" t="str">
-        <v/>
-      </c>
-      <c r="H74" t="str">
-        <v/>
-      </c>
-      <c r="I74" t="str">
-        <v/>
-      </c>
-      <c r="K74" t="str">
-        <v/>
-      </c>
-      <c r="L74" t="str">
-        <v/>
-      </c>
     </row>
     <row r="75">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="E75" t="str">
-        <v/>
-      </c>
-      <c r="F75" t="str">
-        <v/>
-      </c>
-      <c r="G75" t="str">
-        <v/>
-      </c>
-      <c r="H75" t="str">
-        <v/>
-      </c>
-      <c r="I75" t="str">
-        <v/>
-      </c>
-      <c r="K75" t="str">
-        <v/>
-      </c>
-      <c r="L75" t="str">
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C76" t="str">
-        <v/>
-      </c>
-      <c r="E76" t="str">
-        <v/>
-      </c>
-      <c r="F76" t="str">
-        <v/>
-      </c>
-      <c r="G76" t="str">
-        <v/>
-      </c>
-      <c r="H76" t="str">
-        <v/>
-      </c>
-      <c r="I76" t="str">
-        <v/>
-      </c>
-      <c r="K76" t="str">
-        <v/>
-      </c>
-      <c r="L76" t="str">
-        <v/>
-      </c>
     </row>
     <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="E77" t="str">
-        <v/>
-      </c>
-      <c r="F77" t="str">
-        <v/>
-      </c>
-      <c r="G77" t="str">
-        <v/>
-      </c>
-      <c r="H77" t="str">
-        <v/>
-      </c>
-      <c r="I77" t="str">
-        <v/>
-      </c>
-      <c r="K77" t="str">
-        <v/>
-      </c>
-      <c r="L77" t="str">
-        <v/>
-      </c>
     </row>
     <row r="78">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="E78" t="str">
-        <v/>
-      </c>
-      <c r="F78" t="str">
-        <v/>
-      </c>
-      <c r="G78" t="str">
-        <v/>
-      </c>
-      <c r="H78" t="str">
-        <v/>
-      </c>
-      <c r="I78" t="str">
-        <v/>
-      </c>
-      <c r="K78" t="str">
-        <v/>
-      </c>
-      <c r="L78" t="str">
-        <v/>
-      </c>
     </row>
     <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C79" t="str">
-        <v/>
-      </c>
-      <c r="E79" t="str">
-        <v/>
-      </c>
-      <c r="F79" t="str">
-        <v/>
-      </c>
-      <c r="G79" t="str">
-        <v/>
-      </c>
-      <c r="H79" t="str">
-        <v/>
-      </c>
-      <c r="I79" t="str">
-        <v/>
-      </c>
-      <c r="K79" t="str">
-        <v/>
-      </c>
-      <c r="L79" t="str">
-        <v/>
-      </c>
     </row>
     <row r="80">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="E80" t="str">
-        <v/>
-      </c>
-      <c r="F80" t="str">
-        <v/>
-      </c>
-      <c r="G80" t="str">
-        <v/>
-      </c>
-      <c r="H80" t="str">
-        <v/>
-      </c>
-      <c r="I80" t="str">
-        <v/>
-      </c>
-      <c r="K80" t="str">
-        <v/>
-      </c>
-      <c r="L80" t="str">
-        <v/>
-      </c>
     </row>
     <row r="81">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C81" t="str">
-        <v/>
-      </c>
-      <c r="E81" t="str">
-        <v/>
-      </c>
-      <c r="F81" t="str">
-        <v/>
-      </c>
-      <c r="G81" t="str">
-        <v/>
-      </c>
-      <c r="H81" t="str">
-        <v/>
-      </c>
-      <c r="I81" t="str">
-        <v/>
-      </c>
-      <c r="K81" t="str">
-        <v/>
-      </c>
-      <c r="L81" t="str">
-        <v/>
-      </c>
     </row>
     <row r="82">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C82" t="str">
-        <v/>
-      </c>
-      <c r="E82" t="str">
-        <v/>
-      </c>
-      <c r="F82" t="str">
-        <v/>
-      </c>
-      <c r="G82" t="str">
-        <v/>
-      </c>
-      <c r="H82" t="str">
-        <v/>
-      </c>
-      <c r="I82" t="str">
-        <v/>
-      </c>
-      <c r="K82" t="str">
-        <v/>
-      </c>
-      <c r="L82" t="str">
-        <v/>
-      </c>
     </row>
     <row r="83">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C83" t="str">
-        <v/>
-      </c>
-      <c r="E83" t="str">
-        <v/>
-      </c>
-      <c r="F83" t="str">
-        <v/>
-      </c>
-      <c r="G83" t="str">
-        <v/>
-      </c>
-      <c r="H83" t="str">
-        <v/>
-      </c>
-      <c r="I83" t="str">
-        <v/>
-      </c>
-      <c r="K83" t="str">
-        <v/>
-      </c>
-      <c r="L83" t="str">
-        <v/>
-      </c>
     </row>
     <row r="84">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
-      <c r="C84" t="str">
-        <v/>
-      </c>
-      <c r="E84" t="str">
-        <v/>
-      </c>
-      <c r="F84" t="str">
-        <v/>
-      </c>
-      <c r="G84" t="str">
-        <v/>
-      </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-      <c r="I84" t="str">
-        <v/>
-      </c>
-      <c r="K84" t="str">
-        <v/>
-      </c>
-      <c r="L84" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L84"/>
   </ignoredErrors>
@@ -11605,580 +9665,363 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>R5 (6슬롯)</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>R5 (6슬롯)</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>R5 (6슬롯)</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>R5 (6슬롯)</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>R5 (6슬롯)</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>R6 (7슬롯)</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>R7 (8슬롯)</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="str">
-        <v>R8 (10슬롯)</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>R9 (12슬롯)</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="str">
-        <v>R10 (14슬롯)</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="str">
-        <v>R11 (16슬롯)</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L84"/>
   </ignoredErrors>
